--- a/analises/vinhos/tanyno-estoque-setembro-2026.xlsx
+++ b/analises/vinhos/tanyno-estoque-setembro-2026.xlsx
@@ -4,21 +4,21 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9528"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2172" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Autoral" sheetId="1" r:id="rId1"/>
     <sheet name="Signature" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Autoral!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Autoral!$A$1:$L$1</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2278" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="526">
   <si>
     <t>Vinho</t>
   </si>
@@ -1593,6 +1593,9 @@
   </si>
   <si>
     <t>THE TOURIGA NACIONAL</t>
+  </si>
+  <si>
+    <t>venda</t>
   </si>
 </sst>
 </file>
@@ -1602,7 +1605,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1621,13 +1624,32 @@
       <color rgb="FFCC0000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1639,18 +1661,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1928,20 +1955,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:L295"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="69.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.33203125" customWidth="1"/>
     <col min="2" max="2" width="22.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1963,11 +1993,17 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3"/>
+      <c r="I1" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -1989,11 +2025,27 @@
       <c r="G2" s="1">
         <v>90.450450000000004</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
+        <f>G2*1.13</f>
+        <v>102.2090085</v>
+      </c>
+      <c r="I2" s="1">
+        <f>G2*1.6</f>
+        <v>144.72072</v>
+      </c>
+      <c r="J2" s="1">
+        <f>I2*0.92</f>
+        <v>133.14306240000002</v>
+      </c>
+      <c r="K2" s="6">
+        <f>J2/G2</f>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L2">
         <v>2727</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -2015,11 +2067,27 @@
       <c r="G3" s="1">
         <v>76.988849999999999</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
+        <f t="shared" ref="H3:H66" si="0">G3*1.13</f>
+        <v>86.997400499999998</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I66" si="1">G3*1.6</f>
+        <v>123.18216000000001</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" ref="J3:J66" si="2">I3*0.92</f>
+        <v>113.32758720000001</v>
+      </c>
+      <c r="K3" s="6">
+        <f t="shared" ref="K3:K66" si="3">J3/G3</f>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L3">
         <v>2680</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -2041,11 +2109,27 @@
       <c r="G4" s="1">
         <v>76.988849999999999</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
+        <f t="shared" si="0"/>
+        <v>86.997400499999998</v>
+      </c>
+      <c r="I4" s="1">
+        <f t="shared" si="1"/>
+        <v>123.18216000000001</v>
+      </c>
+      <c r="J4" s="1">
+        <f t="shared" si="2"/>
+        <v>113.32758720000001</v>
+      </c>
+      <c r="K4" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L4">
         <v>2656</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>377</v>
       </c>
@@ -2067,12 +2151,28 @@
       <c r="G5" s="1">
         <v>65.998049999999992</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
+        <f t="shared" si="0"/>
+        <v>74.577796499999991</v>
+      </c>
+      <c r="I5" s="1">
+        <f t="shared" si="1"/>
+        <v>105.59688</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" si="2"/>
+        <v>97.149129600000009</v>
+      </c>
+      <c r="K5" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L5">
         <v>1356</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="B6" t="s">
@@ -2093,11 +2193,27 @@
       <c r="G6" s="1">
         <v>118.58774999999999</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
+        <f t="shared" si="0"/>
+        <v>134.00415749999996</v>
+      </c>
+      <c r="I6" s="1">
+        <f t="shared" si="1"/>
+        <v>189.74039999999999</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="2"/>
+        <v>174.56116800000001</v>
+      </c>
+      <c r="K6" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L6">
         <v>1350</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -2119,11 +2235,27 @@
       <c r="G7" s="1">
         <v>105.97815</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
+        <f t="shared" si="0"/>
+        <v>119.75530949999998</v>
+      </c>
+      <c r="I7" s="1">
+        <f t="shared" si="1"/>
+        <v>169.56504000000001</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="2"/>
+        <v>155.99983680000003</v>
+      </c>
+      <c r="K7" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L7">
         <v>1125</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>403</v>
       </c>
@@ -2145,11 +2277,27 @@
       <c r="G8" s="1">
         <v>146.92740000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
+        <f t="shared" si="0"/>
+        <v>166.027962</v>
+      </c>
+      <c r="I8" s="1">
+        <f t="shared" si="1"/>
+        <v>235.08384000000001</v>
+      </c>
+      <c r="J8" s="1">
+        <f t="shared" si="2"/>
+        <v>216.2771328</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L8">
         <v>800</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>409</v>
       </c>
@@ -2171,12 +2319,28 @@
       <c r="G9" s="1">
         <v>146.92740000000001</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
+        <f t="shared" si="0"/>
+        <v>166.027962</v>
+      </c>
+      <c r="I9" s="1">
+        <f t="shared" si="1"/>
+        <v>235.08384000000001</v>
+      </c>
+      <c r="J9" s="1">
+        <f t="shared" si="2"/>
+        <v>216.2771328</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L9">
         <v>720</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>77</v>
       </c>
       <c r="B10" t="s">
@@ -2197,12 +2361,28 @@
       <c r="G10" s="1">
         <v>153.22155000000001</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
+        <f t="shared" si="0"/>
+        <v>173.14035149999998</v>
+      </c>
+      <c r="I10" s="1">
+        <f t="shared" si="1"/>
+        <v>245.15448000000004</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="2"/>
+        <v>225.54212160000003</v>
+      </c>
+      <c r="K10" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L10">
         <v>514</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="7" t="s">
         <v>118</v>
       </c>
       <c r="B11" t="s">
@@ -2223,11 +2403,27 @@
       <c r="G11" s="1">
         <v>186.30045000000001</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
+        <f t="shared" si="0"/>
+        <v>210.5195085</v>
+      </c>
+      <c r="I11" s="1">
+        <f t="shared" si="1"/>
+        <v>298.08072000000004</v>
+      </c>
+      <c r="J11" s="1">
+        <f t="shared" si="2"/>
+        <v>274.23426240000003</v>
+      </c>
+      <c r="K11" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L11">
         <v>455</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -2249,11 +2445,27 @@
       <c r="G12" s="1">
         <v>150.75075000000001</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
+        <f t="shared" si="0"/>
+        <v>170.34834749999999</v>
+      </c>
+      <c r="I12" s="1">
+        <f t="shared" si="1"/>
+        <v>241.20120000000003</v>
+      </c>
+      <c r="J12" s="1">
+        <f t="shared" si="2"/>
+        <v>221.90510400000002</v>
+      </c>
+      <c r="K12" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L12">
         <v>437</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>192</v>
       </c>
@@ -2275,11 +2487,27 @@
       <c r="G13" s="1">
         <v>151.22999999999999</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
+        <f t="shared" si="0"/>
+        <v>170.88989999999998</v>
+      </c>
+      <c r="I13" s="1">
+        <f t="shared" si="1"/>
+        <v>241.96799999999999</v>
+      </c>
+      <c r="J13" s="1">
+        <f t="shared" si="2"/>
+        <v>222.61055999999999</v>
+      </c>
+      <c r="K13" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L13">
         <v>434</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2301,11 +2529,27 @@
       <c r="G14" s="1">
         <v>203.84100000000001</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
+        <f t="shared" si="0"/>
+        <v>230.34032999999999</v>
+      </c>
+      <c r="I14" s="1">
+        <f t="shared" si="1"/>
+        <v>326.14560000000006</v>
+      </c>
+      <c r="J14" s="1">
+        <f t="shared" si="2"/>
+        <v>300.05395200000009</v>
+      </c>
+      <c r="K14" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L14">
         <v>404</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>195</v>
       </c>
@@ -2327,11 +2571,27 @@
       <c r="G15" s="1">
         <v>141.1764</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
+        <f t="shared" si="0"/>
+        <v>159.52933199999998</v>
+      </c>
+      <c r="I15" s="1">
+        <f t="shared" si="1"/>
+        <v>225.88224000000002</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" si="2"/>
+        <v>207.81166080000003</v>
+      </c>
+      <c r="K15" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L15">
         <v>343</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>283</v>
       </c>
@@ -2353,11 +2613,27 @@
       <c r="G16" s="1">
         <v>285.57974999999993</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
+        <f t="shared" si="0"/>
+        <v>322.70511749999991</v>
+      </c>
+      <c r="I16" s="1">
+        <f t="shared" si="1"/>
+        <v>456.92759999999993</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="2"/>
+        <v>420.37339199999997</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L16">
         <v>329</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>218</v>
       </c>
@@ -2379,11 +2655,27 @@
       <c r="G17" s="1">
         <v>249.94484999999997</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
+        <f t="shared" si="0"/>
+        <v>282.43768049999994</v>
+      </c>
+      <c r="I17" s="1">
+        <f t="shared" si="1"/>
+        <v>399.91175999999996</v>
+      </c>
+      <c r="J17" s="1">
+        <f t="shared" si="2"/>
+        <v>367.91881919999997</v>
+      </c>
+      <c r="K17" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L17">
         <v>323</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -2405,11 +2697,27 @@
       <c r="G18" s="1">
         <v>98.76809999999999</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
+        <f t="shared" si="0"/>
+        <v>111.60795299999998</v>
+      </c>
+      <c r="I18" s="1">
+        <f t="shared" si="1"/>
+        <v>158.02895999999998</v>
+      </c>
+      <c r="J18" s="1">
+        <f t="shared" si="2"/>
+        <v>145.38664319999998</v>
+      </c>
+      <c r="K18" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L18">
         <v>288</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>327</v>
       </c>
@@ -2431,11 +2739,27 @@
       <c r="G19" s="1">
         <v>128.87565000000001</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
+        <f t="shared" si="0"/>
+        <v>145.62948449999999</v>
+      </c>
+      <c r="I19" s="1">
+        <f t="shared" si="1"/>
+        <v>206.20104000000003</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" si="2"/>
+        <v>189.70495680000005</v>
+      </c>
+      <c r="K19" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L19">
         <v>282</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2457,11 +2781,27 @@
       <c r="G20" s="1">
         <v>271.67084999999997</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
+        <f t="shared" si="0"/>
+        <v>306.98806049999996</v>
+      </c>
+      <c r="I20" s="1">
+        <f t="shared" si="1"/>
+        <v>434.67336</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="2"/>
+        <v>399.8994912</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L20">
         <v>262</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>77</v>
       </c>
@@ -2483,11 +2823,27 @@
       <c r="G21" s="1">
         <v>153.22155000000001</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
+        <f t="shared" si="0"/>
+        <v>173.14035149999998</v>
+      </c>
+      <c r="I21" s="1">
+        <f t="shared" si="1"/>
+        <v>245.15448000000004</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="2"/>
+        <v>225.54212160000003</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L21">
         <v>245</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>314</v>
       </c>
@@ -2509,11 +2865,27 @@
       <c r="G22" s="1">
         <v>168.18479999999997</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
+        <f t="shared" si="0"/>
+        <v>190.04882399999994</v>
+      </c>
+      <c r="I22" s="1">
+        <f t="shared" si="1"/>
+        <v>269.09567999999996</v>
+      </c>
+      <c r="J22" s="1">
+        <f t="shared" si="2"/>
+        <v>247.56802559999997</v>
+      </c>
+      <c r="K22" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L22">
         <v>241</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>84</v>
       </c>
@@ -2535,11 +2907,27 @@
       <c r="G23" s="1">
         <v>129.73829999999998</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
+        <f t="shared" si="0"/>
+        <v>146.60427899999996</v>
+      </c>
+      <c r="I23" s="1">
+        <f t="shared" si="1"/>
+        <v>207.58127999999999</v>
+      </c>
+      <c r="J23" s="1">
+        <f t="shared" si="2"/>
+        <v>190.97477760000001</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L23">
         <v>237</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>131</v>
       </c>
@@ -2561,11 +2949,27 @@
       <c r="G24" s="1">
         <v>284.98334999999997</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
+        <f t="shared" si="0"/>
+        <v>322.03118549999994</v>
+      </c>
+      <c r="I24" s="1">
+        <f t="shared" si="1"/>
+        <v>455.97335999999996</v>
+      </c>
+      <c r="J24" s="1">
+        <f t="shared" si="2"/>
+        <v>419.4954912</v>
+      </c>
+      <c r="K24" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L24">
         <v>233</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>407</v>
       </c>
@@ -2587,12 +2991,28 @@
       <c r="G25" s="1">
         <v>373.815</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
+        <f t="shared" si="0"/>
+        <v>422.41094999999996</v>
+      </c>
+      <c r="I25" s="1">
+        <f t="shared" si="1"/>
+        <v>598.10400000000004</v>
+      </c>
+      <c r="J25" s="1">
+        <f t="shared" si="2"/>
+        <v>550.2556800000001</v>
+      </c>
+      <c r="K25" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L25">
         <v>231</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
         <v>233</v>
       </c>
       <c r="B26" t="s">
@@ -2613,11 +3033,27 @@
       <c r="G26" s="1">
         <v>220.74254999999999</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
+        <f t="shared" si="0"/>
+        <v>249.43908149999996</v>
+      </c>
+      <c r="I26" s="1">
+        <f t="shared" si="1"/>
+        <v>353.18808000000001</v>
+      </c>
+      <c r="J26" s="1">
+        <f t="shared" si="2"/>
+        <v>324.93303360000004</v>
+      </c>
+      <c r="K26" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L26">
         <v>220</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -2639,11 +3075,27 @@
       <c r="G27" s="1">
         <v>266.03699999999998</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
+        <f t="shared" si="0"/>
+        <v>300.62180999999993</v>
+      </c>
+      <c r="I27" s="1">
+        <f t="shared" si="1"/>
+        <v>425.6592</v>
+      </c>
+      <c r="J27" s="1">
+        <f t="shared" si="2"/>
+        <v>391.60646400000002</v>
+      </c>
+      <c r="K27" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L27">
         <v>216</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>157</v>
       </c>
@@ -2665,11 +3117,27 @@
       <c r="G28" s="1">
         <v>220.43369999999999</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
+        <f t="shared" si="0"/>
+        <v>249.09008099999997</v>
+      </c>
+      <c r="I28" s="1">
+        <f t="shared" si="1"/>
+        <v>352.69391999999999</v>
+      </c>
+      <c r="J28" s="1">
+        <f t="shared" si="2"/>
+        <v>324.47840639999998</v>
+      </c>
+      <c r="K28" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L28">
         <v>211</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>408</v>
       </c>
@@ -2691,11 +3159,27 @@
       <c r="G29" s="1">
         <v>146.92740000000001</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
+        <f t="shared" si="0"/>
+        <v>166.027962</v>
+      </c>
+      <c r="I29" s="1">
+        <f t="shared" si="1"/>
+        <v>235.08384000000001</v>
+      </c>
+      <c r="J29" s="1">
+        <f t="shared" si="2"/>
+        <v>216.2771328</v>
+      </c>
+      <c r="K29" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L29">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>28</v>
       </c>
@@ -2717,11 +3201,27 @@
       <c r="G30" s="1">
         <v>171.9975</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
+        <f t="shared" si="0"/>
+        <v>194.35717499999998</v>
+      </c>
+      <c r="I30" s="1">
+        <f t="shared" si="1"/>
+        <v>275.19600000000003</v>
+      </c>
+      <c r="J30" s="1">
+        <f t="shared" si="2"/>
+        <v>253.18032000000002</v>
+      </c>
+      <c r="K30" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L30">
         <v>201</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>328</v>
       </c>
@@ -2743,11 +3243,27 @@
       <c r="G31" s="1">
         <v>113.47574999999999</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
+        <f t="shared" si="0"/>
+        <v>128.22759749999997</v>
+      </c>
+      <c r="I31" s="1">
+        <f t="shared" si="1"/>
+        <v>181.56119999999999</v>
+      </c>
+      <c r="J31" s="1">
+        <f t="shared" si="2"/>
+        <v>167.036304</v>
+      </c>
+      <c r="K31" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L31">
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>184</v>
       </c>
@@ -2769,11 +3285,27 @@
       <c r="G32" s="1">
         <v>183.19064999999998</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
+        <f t="shared" si="0"/>
+        <v>207.00543449999995</v>
+      </c>
+      <c r="I32" s="1">
+        <f t="shared" si="1"/>
+        <v>293.10503999999997</v>
+      </c>
+      <c r="J32" s="1">
+        <f t="shared" si="2"/>
+        <v>269.6566368</v>
+      </c>
+      <c r="K32" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L32">
         <v>174</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>254</v>
       </c>
@@ -2795,11 +3327,27 @@
       <c r="G33" s="1">
         <v>285.57974999999993</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="1">
+        <f t="shared" si="0"/>
+        <v>322.70511749999991</v>
+      </c>
+      <c r="I33" s="1">
+        <f t="shared" si="1"/>
+        <v>456.92759999999993</v>
+      </c>
+      <c r="J33" s="1">
+        <f t="shared" si="2"/>
+        <v>420.37339199999997</v>
+      </c>
+      <c r="K33" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L33">
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>90</v>
       </c>
@@ -2821,11 +3369,27 @@
       <c r="G34" s="1">
         <v>229.18799999999999</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
+        <f t="shared" si="0"/>
+        <v>258.98243999999994</v>
+      </c>
+      <c r="I34" s="1">
+        <f t="shared" si="1"/>
+        <v>366.70080000000002</v>
+      </c>
+      <c r="J34" s="1">
+        <f t="shared" si="2"/>
+        <v>337.36473600000005</v>
+      </c>
+      <c r="K34" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L34">
         <v>172</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>228</v>
       </c>
@@ -2847,11 +3411,27 @@
       <c r="G35" s="1">
         <v>368.05334999999997</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
+        <f t="shared" si="0"/>
+        <v>415.90028549999994</v>
+      </c>
+      <c r="I35" s="1">
+        <f t="shared" si="1"/>
+        <v>588.88535999999999</v>
+      </c>
+      <c r="J35" s="1">
+        <f t="shared" si="2"/>
+        <v>541.77453120000007</v>
+      </c>
+      <c r="K35" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L35">
         <v>172</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>58</v>
       </c>
@@ -2873,11 +3453,27 @@
       <c r="G36" s="1">
         <v>239.17769999999999</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="1">
+        <f t="shared" si="0"/>
+        <v>270.27080099999995</v>
+      </c>
+      <c r="I36" s="1">
+        <f t="shared" si="1"/>
+        <v>382.68432000000001</v>
+      </c>
+      <c r="J36" s="1">
+        <f t="shared" si="2"/>
+        <v>352.06957440000002</v>
+      </c>
+      <c r="K36" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L36">
         <v>164</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>318</v>
       </c>
@@ -2899,11 +3495,27 @@
       <c r="G37" s="1">
         <v>206.95079999999999</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="1">
+        <f t="shared" si="0"/>
+        <v>233.85440399999996</v>
+      </c>
+      <c r="I37" s="1">
+        <f t="shared" si="1"/>
+        <v>331.12128000000001</v>
+      </c>
+      <c r="J37" s="1">
+        <f t="shared" si="2"/>
+        <v>304.63157760000001</v>
+      </c>
+      <c r="K37" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L37">
         <v>164</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>320</v>
       </c>
@@ -2925,11 +3537,27 @@
       <c r="G38" s="1">
         <v>129.05670000000001</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
+        <f t="shared" si="0"/>
+        <v>145.83407099999999</v>
+      </c>
+      <c r="I38" s="1">
+        <f t="shared" si="1"/>
+        <v>206.49072000000001</v>
+      </c>
+      <c r="J38" s="1">
+        <f t="shared" si="2"/>
+        <v>189.97146240000001</v>
+      </c>
+      <c r="K38" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L38">
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>393</v>
       </c>
@@ -2951,11 +3579,27 @@
       <c r="G39" s="1">
         <v>247.78289999999998</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="1">
+        <f t="shared" si="0"/>
+        <v>279.99467699999997</v>
+      </c>
+      <c r="I39" s="1">
+        <f t="shared" si="1"/>
+        <v>396.45263999999997</v>
+      </c>
+      <c r="J39" s="1">
+        <f t="shared" si="2"/>
+        <v>364.7364288</v>
+      </c>
+      <c r="K39" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L39">
         <v>152</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>137</v>
       </c>
@@ -2977,11 +3621,27 @@
       <c r="G40" s="1">
         <v>192.93539999999999</v>
       </c>
-      <c r="H40">
+      <c r="H40" s="1">
+        <f t="shared" si="0"/>
+        <v>218.01700199999996</v>
+      </c>
+      <c r="I40" s="1">
+        <f t="shared" si="1"/>
+        <v>308.69664</v>
+      </c>
+      <c r="J40" s="1">
+        <f t="shared" si="2"/>
+        <v>284.00090879999999</v>
+      </c>
+      <c r="K40" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L40">
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>134</v>
       </c>
@@ -3003,11 +3663,27 @@
       <c r="G41" s="1">
         <v>181.74224999999998</v>
       </c>
-      <c r="H41">
+      <c r="H41" s="1">
+        <f t="shared" si="0"/>
+        <v>205.36874249999997</v>
+      </c>
+      <c r="I41" s="1">
+        <f t="shared" si="1"/>
+        <v>290.7876</v>
+      </c>
+      <c r="J41" s="1">
+        <f t="shared" si="2"/>
+        <v>267.52459199999998</v>
+      </c>
+      <c r="K41" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L41">
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>197</v>
       </c>
@@ -3029,11 +3705,27 @@
       <c r="G42" s="1">
         <v>255.15270000000001</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
+        <f t="shared" si="0"/>
+        <v>288.32255099999998</v>
+      </c>
+      <c r="I42" s="1">
+        <f t="shared" si="1"/>
+        <v>408.24432000000002</v>
+      </c>
+      <c r="J42" s="1">
+        <f t="shared" si="2"/>
+        <v>375.58477440000001</v>
+      </c>
+      <c r="K42" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L42">
         <v>147</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>312</v>
       </c>
@@ -3055,11 +3747,27 @@
       <c r="G43" s="1">
         <v>244.33229999999998</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
+        <f t="shared" si="0"/>
+        <v>276.09549899999996</v>
+      </c>
+      <c r="I43" s="1">
+        <f t="shared" si="1"/>
+        <v>390.93167999999997</v>
+      </c>
+      <c r="J43" s="1">
+        <f t="shared" si="2"/>
+        <v>359.65714559999998</v>
+      </c>
+      <c r="K43" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L43">
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>406</v>
       </c>
@@ -3081,11 +3789,27 @@
       <c r="G44" s="1">
         <v>330.0222</v>
       </c>
-      <c r="H44">
+      <c r="H44" s="1">
+        <f t="shared" si="0"/>
+        <v>372.92508599999996</v>
+      </c>
+      <c r="I44" s="1">
+        <f t="shared" si="1"/>
+        <v>528.03552000000002</v>
+      </c>
+      <c r="J44" s="1">
+        <f t="shared" si="2"/>
+        <v>485.79267840000006</v>
+      </c>
+      <c r="K44" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L44">
         <v>145</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>303</v>
       </c>
@@ -3107,11 +3831,27 @@
       <c r="G45" s="1">
         <v>164.59575000000001</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="1">
+        <f t="shared" si="0"/>
+        <v>185.99319749999998</v>
+      </c>
+      <c r="I45" s="1">
+        <f t="shared" si="1"/>
+        <v>263.35320000000002</v>
+      </c>
+      <c r="J45" s="1">
+        <f t="shared" si="2"/>
+        <v>242.28494400000002</v>
+      </c>
+      <c r="K45" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L45">
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>217</v>
       </c>
@@ -3133,11 +3873,27 @@
       <c r="G46" s="1">
         <v>249.94484999999997</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="1">
+        <f t="shared" si="0"/>
+        <v>282.43768049999994</v>
+      </c>
+      <c r="I46" s="1">
+        <f t="shared" si="1"/>
+        <v>399.91175999999996</v>
+      </c>
+      <c r="J46" s="1">
+        <f t="shared" si="2"/>
+        <v>367.91881919999997</v>
+      </c>
+      <c r="K46" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L46">
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -3159,11 +3915,27 @@
       <c r="G47" s="1">
         <v>196.66289999999998</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
+        <f t="shared" si="0"/>
+        <v>222.22907699999996</v>
+      </c>
+      <c r="I47" s="1">
+        <f t="shared" si="1"/>
+        <v>314.66064</v>
+      </c>
+      <c r="J47" s="1">
+        <f t="shared" si="2"/>
+        <v>289.48778880000003</v>
+      </c>
+      <c r="K47" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L47">
         <v>129</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>165</v>
       </c>
@@ -3185,11 +3957,27 @@
       <c r="G48" s="1">
         <v>147.6942</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
+        <f t="shared" si="0"/>
+        <v>166.89444599999999</v>
+      </c>
+      <c r="I48" s="1">
+        <f t="shared" si="1"/>
+        <v>236.31072</v>
+      </c>
+      <c r="J48" s="1">
+        <f t="shared" si="2"/>
+        <v>217.40586240000002</v>
+      </c>
+      <c r="K48" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L48">
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>405</v>
       </c>
@@ -3211,11 +3999,27 @@
       <c r="G49" s="1">
         <v>263.72594999999995</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="1">
+        <f t="shared" si="0"/>
+        <v>298.01032349999991</v>
+      </c>
+      <c r="I49" s="1">
+        <f t="shared" si="1"/>
+        <v>421.96151999999995</v>
+      </c>
+      <c r="J49" s="1">
+        <f t="shared" si="2"/>
+        <v>388.20459839999995</v>
+      </c>
+      <c r="K49" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L49">
         <v>127</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>232</v>
       </c>
@@ -3237,11 +4041,27 @@
       <c r="G50" s="1">
         <v>231.45644999999999</v>
       </c>
-      <c r="H50">
+      <c r="H50" s="1">
+        <f t="shared" si="0"/>
+        <v>261.54578849999996</v>
+      </c>
+      <c r="I50" s="1">
+        <f t="shared" si="1"/>
+        <v>370.33032000000003</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" si="2"/>
+        <v>340.70389440000002</v>
+      </c>
+      <c r="K50" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L50">
         <v>126</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>392</v>
       </c>
@@ -3263,11 +4083,27 @@
       <c r="G51" s="1">
         <v>169.44149999999999</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
+        <f t="shared" si="0"/>
+        <v>191.46889499999997</v>
+      </c>
+      <c r="I51" s="1">
+        <f t="shared" si="1"/>
+        <v>271.10640000000001</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" si="2"/>
+        <v>249.417888</v>
+      </c>
+      <c r="K51" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L51">
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>185</v>
       </c>
@@ -3289,11 +4125,27 @@
       <c r="G52" s="1">
         <v>272.87430000000001</v>
       </c>
-      <c r="H52">
+      <c r="H52" s="1">
+        <f t="shared" si="0"/>
+        <v>308.347959</v>
+      </c>
+      <c r="I52" s="1">
+        <f t="shared" si="1"/>
+        <v>436.59888000000001</v>
+      </c>
+      <c r="J52" s="1">
+        <f t="shared" si="2"/>
+        <v>401.67096960000003</v>
+      </c>
+      <c r="K52" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L52">
         <v>121</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>159</v>
       </c>
@@ -3315,11 +4167,27 @@
       <c r="G53" s="1">
         <v>285.57974999999993</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="1">
+        <f t="shared" si="0"/>
+        <v>322.70511749999991</v>
+      </c>
+      <c r="I53" s="1">
+        <f t="shared" si="1"/>
+        <v>456.92759999999993</v>
+      </c>
+      <c r="J53" s="1">
+        <f t="shared" si="2"/>
+        <v>420.37339199999997</v>
+      </c>
+      <c r="K53" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L53">
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>155</v>
       </c>
@@ -3341,11 +4209,27 @@
       <c r="G54" s="1">
         <v>341.40704999999997</v>
       </c>
-      <c r="H54">
+      <c r="H54" s="1">
+        <f t="shared" si="0"/>
+        <v>385.78996649999993</v>
+      </c>
+      <c r="I54" s="1">
+        <f t="shared" si="1"/>
+        <v>546.25127999999995</v>
+      </c>
+      <c r="J54" s="1">
+        <f t="shared" si="2"/>
+        <v>502.55117759999996</v>
+      </c>
+      <c r="K54" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L54">
         <v>117</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -3367,11 +4251,27 @@
       <c r="G55" s="1">
         <v>251.85119999999998</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="1">
+        <f t="shared" si="0"/>
+        <v>284.59185599999995</v>
+      </c>
+      <c r="I55" s="1">
+        <f t="shared" si="1"/>
+        <v>402.96191999999996</v>
+      </c>
+      <c r="J55" s="1">
+        <f t="shared" si="2"/>
+        <v>370.72496639999997</v>
+      </c>
+      <c r="K55" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L55">
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>166</v>
       </c>
@@ -3393,11 +4293,27 @@
       <c r="G56" s="1">
         <v>277.8372</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="1">
+        <f t="shared" si="0"/>
+        <v>313.95603599999998</v>
+      </c>
+      <c r="I56" s="1">
+        <f t="shared" si="1"/>
+        <v>444.53952000000004</v>
+      </c>
+      <c r="J56" s="1">
+        <f t="shared" si="2"/>
+        <v>408.97635840000004</v>
+      </c>
+      <c r="K56" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L56">
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -3419,11 +4335,27 @@
       <c r="G57" s="1">
         <v>271.67084999999997</v>
       </c>
-      <c r="H57">
+      <c r="H57" s="1">
+        <f t="shared" si="0"/>
+        <v>306.98806049999996</v>
+      </c>
+      <c r="I57" s="1">
+        <f t="shared" si="1"/>
+        <v>434.67336</v>
+      </c>
+      <c r="J57" s="1">
+        <f t="shared" si="2"/>
+        <v>399.8994912</v>
+      </c>
+      <c r="K57" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L57">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>160</v>
       </c>
@@ -3445,11 +4377,27 @@
       <c r="G58" s="1">
         <v>324.31379999999996</v>
       </c>
-      <c r="H58">
+      <c r="H58" s="1">
+        <f t="shared" si="0"/>
+        <v>366.47459399999991</v>
+      </c>
+      <c r="I58" s="1">
+        <f t="shared" si="1"/>
+        <v>518.90207999999996</v>
+      </c>
+      <c r="J58" s="1">
+        <f t="shared" si="2"/>
+        <v>477.3899136</v>
+      </c>
+      <c r="K58" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L58">
         <v>111</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>171</v>
       </c>
@@ -3471,11 +4419,27 @@
       <c r="G59" s="1">
         <v>291.91649999999998</v>
       </c>
-      <c r="H59">
+      <c r="H59" s="1">
+        <f t="shared" si="0"/>
+        <v>329.86564499999997</v>
+      </c>
+      <c r="I59" s="1">
+        <f t="shared" si="1"/>
+        <v>467.06639999999999</v>
+      </c>
+      <c r="J59" s="1">
+        <f t="shared" si="2"/>
+        <v>429.70108800000003</v>
+      </c>
+      <c r="K59" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L59">
         <v>111</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>139</v>
       </c>
@@ -3497,11 +4461,27 @@
       <c r="G60" s="1">
         <v>248.90115</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="1">
+        <f t="shared" si="0"/>
+        <v>281.25829949999996</v>
+      </c>
+      <c r="I60" s="1">
+        <f t="shared" si="1"/>
+        <v>398.24184000000002</v>
+      </c>
+      <c r="J60" s="1">
+        <f t="shared" si="2"/>
+        <v>366.38249280000002</v>
+      </c>
+      <c r="K60" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L60">
         <v>110</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>343</v>
       </c>
@@ -3523,11 +4503,27 @@
       <c r="G61" s="1">
         <v>98.618999999999986</v>
       </c>
-      <c r="H61">
+      <c r="H61" s="1">
+        <f t="shared" si="0"/>
+        <v>111.43946999999997</v>
+      </c>
+      <c r="I61" s="1">
+        <f t="shared" si="1"/>
+        <v>157.79039999999998</v>
+      </c>
+      <c r="J61" s="1">
+        <f t="shared" si="2"/>
+        <v>145.16716799999998</v>
+      </c>
+      <c r="K61" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L61">
         <v>110</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>170</v>
       </c>
@@ -3549,11 +4545,27 @@
       <c r="G62" s="1">
         <v>244.33229999999998</v>
       </c>
-      <c r="H62">
+      <c r="H62" s="1">
+        <f t="shared" si="0"/>
+        <v>276.09549899999996</v>
+      </c>
+      <c r="I62" s="1">
+        <f t="shared" si="1"/>
+        <v>390.93167999999997</v>
+      </c>
+      <c r="J62" s="1">
+        <f t="shared" si="2"/>
+        <v>359.65714559999998</v>
+      </c>
+      <c r="K62" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L62">
         <v>108</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -3575,11 +4587,27 @@
       <c r="G63" s="1">
         <v>201.21045000000001</v>
       </c>
-      <c r="H63">
+      <c r="H63" s="1">
+        <f t="shared" si="0"/>
+        <v>227.3678085</v>
+      </c>
+      <c r="I63" s="1">
+        <f t="shared" si="1"/>
+        <v>321.93672000000004</v>
+      </c>
+      <c r="J63" s="1">
+        <f t="shared" si="2"/>
+        <v>296.18178240000003</v>
+      </c>
+      <c r="K63" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L63">
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>306</v>
       </c>
@@ -3601,11 +4629,27 @@
       <c r="G64" s="1">
         <v>244.63049999999998</v>
       </c>
-      <c r="H64">
+      <c r="H64" s="1">
+        <f t="shared" si="0"/>
+        <v>276.43246499999998</v>
+      </c>
+      <c r="I64" s="1">
+        <f t="shared" si="1"/>
+        <v>391.40879999999999</v>
+      </c>
+      <c r="J64" s="1">
+        <f t="shared" si="2"/>
+        <v>360.09609599999999</v>
+      </c>
+      <c r="K64" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L64">
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>132</v>
       </c>
@@ -3627,11 +4671,27 @@
       <c r="G65" s="1">
         <v>488.65394999999995</v>
       </c>
-      <c r="H65">
+      <c r="H65" s="1">
+        <f t="shared" si="0"/>
+        <v>552.1789634999999</v>
+      </c>
+      <c r="I65" s="1">
+        <f t="shared" si="1"/>
+        <v>781.84631999999999</v>
+      </c>
+      <c r="J65" s="1">
+        <f t="shared" si="2"/>
+        <v>719.29861440000002</v>
+      </c>
+      <c r="K65" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L65">
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>339</v>
       </c>
@@ -3653,11 +4713,27 @@
       <c r="G66" s="1">
         <v>132.15584999999999</v>
       </c>
-      <c r="H66">
+      <c r="H66" s="1">
+        <f t="shared" si="0"/>
+        <v>149.33611049999996</v>
+      </c>
+      <c r="I66" s="1">
+        <f t="shared" si="1"/>
+        <v>211.44935999999998</v>
+      </c>
+      <c r="J66" s="1">
+        <f t="shared" si="2"/>
+        <v>194.53341119999999</v>
+      </c>
+      <c r="K66" s="6">
+        <f t="shared" si="3"/>
+        <v>1.472</v>
+      </c>
+      <c r="L66">
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>215</v>
       </c>
@@ -3679,11 +4755,27 @@
       <c r="G67" s="1">
         <v>750.87824999999987</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="1">
+        <f t="shared" ref="H67:H130" si="4">G67*1.13</f>
+        <v>848.49242249999975</v>
+      </c>
+      <c r="I67" s="1">
+        <f t="shared" ref="I67:I130" si="5">G67*1.6</f>
+        <v>1201.4051999999999</v>
+      </c>
+      <c r="J67" s="1">
+        <f t="shared" ref="J67:J130" si="6">I67*0.92</f>
+        <v>1105.292784</v>
+      </c>
+      <c r="K67" s="6">
+        <f t="shared" ref="K67:K130" si="7">J67/G67</f>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L67">
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -3705,11 +4797,27 @@
       <c r="G68" s="1">
         <v>272.87430000000001</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
+        <f t="shared" si="4"/>
+        <v>308.347959</v>
+      </c>
+      <c r="I68" s="1">
+        <f t="shared" si="5"/>
+        <v>436.59888000000001</v>
+      </c>
+      <c r="J68" s="1">
+        <f t="shared" si="6"/>
+        <v>401.67096960000003</v>
+      </c>
+      <c r="K68" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L68">
         <v>97</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>101</v>
       </c>
@@ -3731,11 +4839,27 @@
       <c r="G69" s="1">
         <v>181.15649999999999</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="1">
+        <f t="shared" si="4"/>
+        <v>204.70684499999999</v>
+      </c>
+      <c r="I69" s="1">
+        <f t="shared" si="5"/>
+        <v>289.85039999999998</v>
+      </c>
+      <c r="J69" s="1">
+        <f t="shared" si="6"/>
+        <v>266.66236800000001</v>
+      </c>
+      <c r="K69" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L69">
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>347</v>
       </c>
@@ -3757,11 +4881,27 @@
       <c r="G70" s="1">
         <v>495.45929999999998</v>
       </c>
-      <c r="H70">
+      <c r="H70" s="1">
+        <f t="shared" si="4"/>
+        <v>559.86900899999989</v>
+      </c>
+      <c r="I70" s="1">
+        <f t="shared" si="5"/>
+        <v>792.73487999999998</v>
+      </c>
+      <c r="J70" s="1">
+        <f t="shared" si="6"/>
+        <v>729.31608960000005</v>
+      </c>
+      <c r="K70" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L70">
         <v>94</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>196</v>
       </c>
@@ -3783,11 +4923,27 @@
       <c r="G71" s="1">
         <v>315.20805000000001</v>
       </c>
-      <c r="H71">
+      <c r="H71" s="1">
+        <f t="shared" si="4"/>
+        <v>356.18509649999999</v>
+      </c>
+      <c r="I71" s="1">
+        <f t="shared" si="5"/>
+        <v>504.33288000000005</v>
+      </c>
+      <c r="J71" s="1">
+        <f t="shared" si="6"/>
+        <v>463.98624960000006</v>
+      </c>
+      <c r="K71" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L71">
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>194</v>
       </c>
@@ -3809,11 +4965,27 @@
       <c r="G72" s="1">
         <v>357.78674999999998</v>
       </c>
-      <c r="H72">
+      <c r="H72" s="1">
+        <f t="shared" si="4"/>
+        <v>404.29902749999997</v>
+      </c>
+      <c r="I72" s="1">
+        <f t="shared" si="5"/>
+        <v>572.4588</v>
+      </c>
+      <c r="J72" s="1">
+        <f t="shared" si="6"/>
+        <v>526.66209600000002</v>
+      </c>
+      <c r="K72" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L72">
         <v>90</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>397</v>
       </c>
@@ -3835,11 +5007,27 @@
       <c r="G73" s="1">
         <v>149.85615000000001</v>
       </c>
-      <c r="H73">
+      <c r="H73" s="1">
+        <f t="shared" si="4"/>
+        <v>169.33744949999999</v>
+      </c>
+      <c r="I73" s="1">
+        <f t="shared" si="5"/>
+        <v>239.76984000000004</v>
+      </c>
+      <c r="J73" s="1">
+        <f t="shared" si="6"/>
+        <v>220.58825280000005</v>
+      </c>
+      <c r="K73" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L73">
         <v>89</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>172</v>
       </c>
@@ -3861,11 +5049,27 @@
       <c r="G74" s="1">
         <v>272.87430000000001</v>
       </c>
-      <c r="H74">
+      <c r="H74" s="1">
+        <f t="shared" si="4"/>
+        <v>308.347959</v>
+      </c>
+      <c r="I74" s="1">
+        <f t="shared" si="5"/>
+        <v>436.59888000000001</v>
+      </c>
+      <c r="J74" s="1">
+        <f t="shared" si="6"/>
+        <v>401.67096960000003</v>
+      </c>
+      <c r="K74" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L74">
         <v>88</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>380</v>
       </c>
@@ -3887,11 +5091,27 @@
       <c r="G75" s="1">
         <v>306.5283</v>
       </c>
-      <c r="H75">
+      <c r="H75" s="1">
+        <f t="shared" si="4"/>
+        <v>346.37697899999995</v>
+      </c>
+      <c r="I75" s="1">
+        <f t="shared" si="5"/>
+        <v>490.44528000000003</v>
+      </c>
+      <c r="J75" s="1">
+        <f t="shared" si="6"/>
+        <v>451.20965760000007</v>
+      </c>
+      <c r="K75" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L75">
         <v>88</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>389</v>
       </c>
@@ -3913,11 +5133,27 @@
       <c r="G76" s="1">
         <v>345.68834999999996</v>
       </c>
-      <c r="H76">
+      <c r="H76" s="1">
+        <f t="shared" si="4"/>
+        <v>390.62783549999989</v>
+      </c>
+      <c r="I76" s="1">
+        <f t="shared" si="5"/>
+        <v>553.10136</v>
+      </c>
+      <c r="J76" s="1">
+        <f t="shared" si="6"/>
+        <v>508.85325120000005</v>
+      </c>
+      <c r="K76" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L76">
         <v>88</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>367</v>
       </c>
@@ -3939,11 +5175,27 @@
       <c r="G77" s="1">
         <v>231.96764999999999</v>
       </c>
-      <c r="H77">
+      <c r="H77" s="1">
+        <f t="shared" si="4"/>
+        <v>262.12344449999995</v>
+      </c>
+      <c r="I77" s="1">
+        <f t="shared" si="5"/>
+        <v>371.14823999999999</v>
+      </c>
+      <c r="J77" s="1">
+        <f t="shared" si="6"/>
+        <v>341.45638079999998</v>
+      </c>
+      <c r="K77" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L77">
         <v>87</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>388</v>
       </c>
@@ -3965,11 +5217,27 @@
       <c r="G78" s="1">
         <v>345.68834999999996</v>
       </c>
-      <c r="H78">
+      <c r="H78" s="1">
+        <f t="shared" si="4"/>
+        <v>390.62783549999989</v>
+      </c>
+      <c r="I78" s="1">
+        <f t="shared" si="5"/>
+        <v>553.10136</v>
+      </c>
+      <c r="J78" s="1">
+        <f t="shared" si="6"/>
+        <v>508.85325120000005</v>
+      </c>
+      <c r="K78" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L78">
         <v>87</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>384</v>
       </c>
@@ -3991,11 +5259,27 @@
       <c r="G79" s="1">
         <v>247.78289999999998</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="1">
+        <f t="shared" si="4"/>
+        <v>279.99467699999997</v>
+      </c>
+      <c r="I79" s="1">
+        <f t="shared" si="5"/>
+        <v>396.45263999999997</v>
+      </c>
+      <c r="J79" s="1">
+        <f t="shared" si="6"/>
+        <v>364.7364288</v>
+      </c>
+      <c r="K79" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L79">
         <v>85</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>386</v>
       </c>
@@ -4017,11 +5301,27 @@
       <c r="G80" s="1">
         <v>247.78289999999998</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="1">
+        <f t="shared" si="4"/>
+        <v>279.99467699999997</v>
+      </c>
+      <c r="I80" s="1">
+        <f t="shared" si="5"/>
+        <v>396.45263999999997</v>
+      </c>
+      <c r="J80" s="1">
+        <f t="shared" si="6"/>
+        <v>364.7364288</v>
+      </c>
+      <c r="K80" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L80">
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>173</v>
       </c>
@@ -4043,11 +5343,27 @@
       <c r="G81" s="1">
         <v>283.52430000000004</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="1">
+        <f t="shared" si="4"/>
+        <v>320.38245900000004</v>
+      </c>
+      <c r="I81" s="1">
+        <f t="shared" si="5"/>
+        <v>453.63888000000009</v>
+      </c>
+      <c r="J81" s="1">
+        <f t="shared" si="6"/>
+        <v>417.34776960000011</v>
+      </c>
+      <c r="K81" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L81">
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>202</v>
       </c>
@@ -4069,11 +5385,27 @@
       <c r="G82" s="1">
         <v>348.48930000000001</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="1">
+        <f t="shared" si="4"/>
+        <v>393.79290899999995</v>
+      </c>
+      <c r="I82" s="1">
+        <f t="shared" si="5"/>
+        <v>557.58288000000005</v>
+      </c>
+      <c r="J82" s="1">
+        <f t="shared" si="6"/>
+        <v>512.97624960000007</v>
+      </c>
+      <c r="K82" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L82">
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>90</v>
       </c>
@@ -4095,11 +5427,27 @@
       <c r="G83" s="1">
         <v>304.90949999999998</v>
       </c>
-      <c r="H83">
+      <c r="H83" s="1">
+        <f t="shared" si="4"/>
+        <v>344.54773499999993</v>
+      </c>
+      <c r="I83" s="1">
+        <f t="shared" si="5"/>
+        <v>487.85519999999997</v>
+      </c>
+      <c r="J83" s="1">
+        <f t="shared" si="6"/>
+        <v>448.82678399999998</v>
+      </c>
+      <c r="K83" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L83">
         <v>84</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>387</v>
       </c>
@@ -4121,11 +5469,27 @@
       <c r="G84" s="1">
         <v>247.78289999999998</v>
       </c>
-      <c r="H84">
+      <c r="H84" s="1">
+        <f t="shared" si="4"/>
+        <v>279.99467699999997</v>
+      </c>
+      <c r="I84" s="1">
+        <f t="shared" si="5"/>
+        <v>396.45263999999997</v>
+      </c>
+      <c r="J84" s="1">
+        <f t="shared" si="6"/>
+        <v>364.7364288</v>
+      </c>
+      <c r="K84" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L84">
         <v>84</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>97</v>
       </c>
@@ -4147,11 +5511,27 @@
       <c r="G85" s="1">
         <v>246.22799999999998</v>
       </c>
-      <c r="H85">
+      <c r="H85" s="1">
+        <f t="shared" si="4"/>
+        <v>278.23763999999994</v>
+      </c>
+      <c r="I85" s="1">
+        <f t="shared" si="5"/>
+        <v>393.96479999999997</v>
+      </c>
+      <c r="J85" s="1">
+        <f t="shared" si="6"/>
+        <v>362.44761599999998</v>
+      </c>
+      <c r="K85" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L85">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>187</v>
       </c>
@@ -4173,11 +5553,27 @@
       <c r="G86" s="1">
         <v>253.84275</v>
       </c>
-      <c r="H86">
+      <c r="H86" s="1">
+        <f t="shared" si="4"/>
+        <v>286.84230749999995</v>
+      </c>
+      <c r="I86" s="1">
+        <f t="shared" si="5"/>
+        <v>406.14840000000004</v>
+      </c>
+      <c r="J86" s="1">
+        <f t="shared" si="6"/>
+        <v>373.65652800000004</v>
+      </c>
+      <c r="K86" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L86">
         <v>83</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>226</v>
       </c>
@@ -4199,11 +5595,27 @@
       <c r="G87" s="1">
         <v>291.91649999999998</v>
       </c>
-      <c r="H87">
+      <c r="H87" s="1">
+        <f t="shared" si="4"/>
+        <v>329.86564499999997</v>
+      </c>
+      <c r="I87" s="1">
+        <f t="shared" si="5"/>
+        <v>467.06639999999999</v>
+      </c>
+      <c r="J87" s="1">
+        <f t="shared" si="6"/>
+        <v>429.70108800000003</v>
+      </c>
+      <c r="K87" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L87">
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>164</v>
       </c>
@@ -4225,11 +5637,27 @@
       <c r="G88" s="1">
         <v>147.6942</v>
       </c>
-      <c r="H88">
+      <c r="H88" s="1">
+        <f t="shared" si="4"/>
+        <v>166.89444599999999</v>
+      </c>
+      <c r="I88" s="1">
+        <f t="shared" si="5"/>
+        <v>236.31072</v>
+      </c>
+      <c r="J88" s="1">
+        <f t="shared" si="6"/>
+        <v>217.40586240000002</v>
+      </c>
+      <c r="K88" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L88">
         <v>79</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>264</v>
       </c>
@@ -4251,11 +5679,27 @@
       <c r="G89" s="1">
         <v>283.4391</v>
       </c>
-      <c r="H89">
+      <c r="H89" s="1">
+        <f t="shared" si="4"/>
+        <v>320.28618299999994</v>
+      </c>
+      <c r="I89" s="1">
+        <f t="shared" si="5"/>
+        <v>453.50256000000002</v>
+      </c>
+      <c r="J89" s="1">
+        <f t="shared" si="6"/>
+        <v>417.22235520000004</v>
+      </c>
+      <c r="K89" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L89">
         <v>79</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>200</v>
       </c>
@@ -4277,11 +5721,27 @@
       <c r="G90" s="1">
         <v>348.48930000000001</v>
       </c>
-      <c r="H90">
+      <c r="H90" s="1">
+        <f t="shared" si="4"/>
+        <v>393.79290899999995</v>
+      </c>
+      <c r="I90" s="1">
+        <f t="shared" si="5"/>
+        <v>557.58288000000005</v>
+      </c>
+      <c r="J90" s="1">
+        <f t="shared" si="6"/>
+        <v>512.97624960000007</v>
+      </c>
+      <c r="K90" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L90">
         <v>78</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>248</v>
       </c>
@@ -4303,11 +5763,27 @@
       <c r="G91" s="1">
         <v>528.70859999999993</v>
       </c>
-      <c r="H91">
+      <c r="H91" s="1">
+        <f t="shared" si="4"/>
+        <v>597.44071799999983</v>
+      </c>
+      <c r="I91" s="1">
+        <f t="shared" si="5"/>
+        <v>845.93375999999989</v>
+      </c>
+      <c r="J91" s="1">
+        <f t="shared" si="6"/>
+        <v>778.25905919999991</v>
+      </c>
+      <c r="K91" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L91">
         <v>78</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>55</v>
       </c>
@@ -4329,11 +5805,27 @@
       <c r="G92" s="1">
         <v>266.03699999999998</v>
       </c>
-      <c r="H92">
+      <c r="H92" s="1">
+        <f t="shared" si="4"/>
+        <v>300.62180999999993</v>
+      </c>
+      <c r="I92" s="1">
+        <f t="shared" si="5"/>
+        <v>425.6592</v>
+      </c>
+      <c r="J92" s="1">
+        <f t="shared" si="6"/>
+        <v>391.60646400000002</v>
+      </c>
+      <c r="K92" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L92">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>399</v>
       </c>
@@ -4355,11 +5847,27 @@
       <c r="G93" s="1">
         <v>172.1892</v>
       </c>
-      <c r="H93">
+      <c r="H93" s="1">
+        <f t="shared" si="4"/>
+        <v>194.57379599999999</v>
+      </c>
+      <c r="I93" s="1">
+        <f t="shared" si="5"/>
+        <v>275.50272000000001</v>
+      </c>
+      <c r="J93" s="1">
+        <f t="shared" si="6"/>
+        <v>253.46250240000003</v>
+      </c>
+      <c r="K93" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L93">
         <v>77</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>169</v>
       </c>
@@ -4381,11 +5889,27 @@
       <c r="G94" s="1">
         <v>253.84275</v>
       </c>
-      <c r="H94">
+      <c r="H94" s="1">
+        <f t="shared" si="4"/>
+        <v>286.84230749999995</v>
+      </c>
+      <c r="I94" s="1">
+        <f t="shared" si="5"/>
+        <v>406.14840000000004</v>
+      </c>
+      <c r="J94" s="1">
+        <f t="shared" si="6"/>
+        <v>373.65652800000004</v>
+      </c>
+      <c r="K94" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L94">
         <v>76</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>391</v>
       </c>
@@ -4407,11 +5931,27 @@
       <c r="G95" s="1">
         <v>169.44149999999999</v>
       </c>
-      <c r="H95">
+      <c r="H95" s="1">
+        <f t="shared" si="4"/>
+        <v>191.46889499999997</v>
+      </c>
+      <c r="I95" s="1">
+        <f t="shared" si="5"/>
+        <v>271.10640000000001</v>
+      </c>
+      <c r="J95" s="1">
+        <f t="shared" si="6"/>
+        <v>249.417888</v>
+      </c>
+      <c r="K95" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L95">
         <v>76</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>110</v>
       </c>
@@ -4433,11 +5973,27 @@
       <c r="G96" s="1">
         <v>345.45405</v>
       </c>
-      <c r="H96">
+      <c r="H96" s="1">
+        <f t="shared" si="4"/>
+        <v>390.36307649999998</v>
+      </c>
+      <c r="I96" s="1">
+        <f t="shared" si="5"/>
+        <v>552.72648000000004</v>
+      </c>
+      <c r="J96" s="1">
+        <f t="shared" si="6"/>
+        <v>508.50836160000006</v>
+      </c>
+      <c r="K96" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L96">
         <v>73</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -4459,11 +6015,27 @@
       <c r="G97" s="1">
         <v>129.37620000000001</v>
       </c>
-      <c r="H97">
+      <c r="H97" s="1">
+        <f t="shared" si="4"/>
+        <v>146.19510600000001</v>
+      </c>
+      <c r="I97" s="1">
+        <f t="shared" si="5"/>
+        <v>207.00192000000004</v>
+      </c>
+      <c r="J97" s="1">
+        <f t="shared" si="6"/>
+        <v>190.44176640000003</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L97">
         <v>73</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>229</v>
       </c>
@@ -4485,11 +6057,27 @@
       <c r="G98" s="1">
         <v>368.05334999999997</v>
       </c>
-      <c r="H98">
+      <c r="H98" s="1">
+        <f t="shared" si="4"/>
+        <v>415.90028549999994</v>
+      </c>
+      <c r="I98" s="1">
+        <f t="shared" si="5"/>
+        <v>588.88535999999999</v>
+      </c>
+      <c r="J98" s="1">
+        <f t="shared" si="6"/>
+        <v>541.77453120000007</v>
+      </c>
+      <c r="K98" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L98">
         <v>72</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>250</v>
       </c>
@@ -4511,11 +6099,27 @@
       <c r="G99" s="1">
         <v>377.57444999999996</v>
       </c>
-      <c r="H99">
+      <c r="H99" s="1">
+        <f t="shared" si="4"/>
+        <v>426.65912849999989</v>
+      </c>
+      <c r="I99" s="1">
+        <f t="shared" si="5"/>
+        <v>604.11911999999995</v>
+      </c>
+      <c r="J99" s="1">
+        <f t="shared" si="6"/>
+        <v>555.78959039999995</v>
+      </c>
+      <c r="K99" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L99">
         <v>72</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>325</v>
       </c>
@@ -4537,11 +6141,27 @@
       <c r="G100" s="1">
         <v>142.47569999999999</v>
       </c>
-      <c r="H100">
+      <c r="H100" s="1">
+        <f t="shared" si="4"/>
+        <v>160.99754099999998</v>
+      </c>
+      <c r="I100" s="1">
+        <f t="shared" si="5"/>
+        <v>227.96111999999999</v>
+      </c>
+      <c r="J100" s="1">
+        <f t="shared" si="6"/>
+        <v>209.72423040000001</v>
+      </c>
+      <c r="K100" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L100">
         <v>72</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>64</v>
       </c>
@@ -4563,11 +6183,27 @@
       <c r="G101" s="1">
         <v>264.24779999999998</v>
       </c>
-      <c r="H101">
+      <c r="H101" s="1">
+        <f t="shared" si="4"/>
+        <v>298.60001399999993</v>
+      </c>
+      <c r="I101" s="1">
+        <f t="shared" si="5"/>
+        <v>422.79647999999997</v>
+      </c>
+      <c r="J101" s="1">
+        <f t="shared" si="6"/>
+        <v>388.97276160000001</v>
+      </c>
+      <c r="K101" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L101">
         <v>71</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>188</v>
       </c>
@@ -4589,11 +6225,27 @@
       <c r="G102" s="1">
         <v>339.50069999999994</v>
       </c>
-      <c r="H102">
+      <c r="H102" s="1">
+        <f t="shared" si="4"/>
+        <v>383.63579099999987</v>
+      </c>
+      <c r="I102" s="1">
+        <f t="shared" si="5"/>
+        <v>543.20111999999995</v>
+      </c>
+      <c r="J102" s="1">
+        <f t="shared" si="6"/>
+        <v>499.74503039999996</v>
+      </c>
+      <c r="K102" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L102">
         <v>69</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>346</v>
       </c>
@@ -4615,11 +6267,27 @@
       <c r="G103" s="1">
         <v>441.11234999999999</v>
       </c>
-      <c r="H103">
+      <c r="H103" s="1">
+        <f t="shared" si="4"/>
+        <v>498.45695549999994</v>
+      </c>
+      <c r="I103" s="1">
+        <f t="shared" si="5"/>
+        <v>705.77976000000001</v>
+      </c>
+      <c r="J103" s="1">
+        <f t="shared" si="6"/>
+        <v>649.3173792</v>
+      </c>
+      <c r="K103" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L103">
         <v>69</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>390</v>
       </c>
@@ -4641,11 +6309,27 @@
       <c r="G104" s="1">
         <v>169.44149999999999</v>
       </c>
-      <c r="H104">
+      <c r="H104" s="1">
+        <f t="shared" si="4"/>
+        <v>191.46889499999997</v>
+      </c>
+      <c r="I104" s="1">
+        <f t="shared" si="5"/>
+        <v>271.10640000000001</v>
+      </c>
+      <c r="J104" s="1">
+        <f t="shared" si="6"/>
+        <v>249.417888</v>
+      </c>
+      <c r="K104" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L104">
         <v>69</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>78</v>
       </c>
@@ -4667,11 +6351,27 @@
       <c r="G105" s="1">
         <v>260.6694</v>
       </c>
-      <c r="H105">
+      <c r="H105" s="1">
+        <f t="shared" si="4"/>
+        <v>294.55642199999994</v>
+      </c>
+      <c r="I105" s="1">
+        <f t="shared" si="5"/>
+        <v>417.07104000000004</v>
+      </c>
+      <c r="J105" s="1">
+        <f t="shared" si="6"/>
+        <v>383.70535680000006</v>
+      </c>
+      <c r="K105" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L105">
         <v>68</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>289</v>
       </c>
@@ -4693,11 +6393,27 @@
       <c r="G106" s="1">
         <v>843.94860000000006</v>
       </c>
-      <c r="H106">
+      <c r="H106" s="1">
+        <f t="shared" si="4"/>
+        <v>953.66191800000001</v>
+      </c>
+      <c r="I106" s="1">
+        <f t="shared" si="5"/>
+        <v>1350.3177600000001</v>
+      </c>
+      <c r="J106" s="1">
+        <f t="shared" si="6"/>
+        <v>1242.2923392000002</v>
+      </c>
+      <c r="K106" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L106">
         <v>68</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>321</v>
       </c>
@@ -4719,11 +6435,27 @@
       <c r="G107" s="1">
         <v>185.99159999999998</v>
       </c>
-      <c r="H107">
+      <c r="H107" s="1">
+        <f t="shared" si="4"/>
+        <v>210.17050799999996</v>
+      </c>
+      <c r="I107" s="1">
+        <f t="shared" si="5"/>
+        <v>297.58655999999996</v>
+      </c>
+      <c r="J107" s="1">
+        <f t="shared" si="6"/>
+        <v>273.77963519999997</v>
+      </c>
+      <c r="K107" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L107">
         <v>68</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>158</v>
       </c>
@@ -4745,11 +6477,27 @@
       <c r="G108" s="1">
         <v>490.31534999999997</v>
       </c>
-      <c r="H108">
+      <c r="H108" s="1">
+        <f t="shared" si="4"/>
+        <v>554.05634549999991</v>
+      </c>
+      <c r="I108" s="1">
+        <f t="shared" si="5"/>
+        <v>784.50455999999997</v>
+      </c>
+      <c r="J108" s="1">
+        <f t="shared" si="6"/>
+        <v>721.74419520000004</v>
+      </c>
+      <c r="K108" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L108">
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>266</v>
       </c>
@@ -4771,11 +6519,27 @@
       <c r="G109" s="1">
         <v>329.92635000000001</v>
       </c>
-      <c r="H109">
+      <c r="H109" s="1">
+        <f t="shared" si="4"/>
+        <v>372.81677550000001</v>
+      </c>
+      <c r="I109" s="1">
+        <f t="shared" si="5"/>
+        <v>527.88216</v>
+      </c>
+      <c r="J109" s="1">
+        <f t="shared" si="6"/>
+        <v>485.65158719999999</v>
+      </c>
+      <c r="K109" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L109">
         <v>65</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>285</v>
       </c>
@@ -4797,11 +6561,27 @@
       <c r="G110" s="1">
         <v>750.87824999999987</v>
       </c>
-      <c r="H110">
+      <c r="H110" s="1">
+        <f t="shared" si="4"/>
+        <v>848.49242249999975</v>
+      </c>
+      <c r="I110" s="1">
+        <f t="shared" si="5"/>
+        <v>1201.4051999999999</v>
+      </c>
+      <c r="J110" s="1">
+        <f t="shared" si="6"/>
+        <v>1105.292784</v>
+      </c>
+      <c r="K110" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L110">
         <v>65</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>350</v>
       </c>
@@ -4823,11 +6603,27 @@
       <c r="G111" s="1">
         <v>355.48635000000002</v>
       </c>
-      <c r="H111">
+      <c r="H111" s="1">
+        <f t="shared" si="4"/>
+        <v>401.69957549999998</v>
+      </c>
+      <c r="I111" s="1">
+        <f t="shared" si="5"/>
+        <v>568.77816000000007</v>
+      </c>
+      <c r="J111" s="1">
+        <f t="shared" si="6"/>
+        <v>523.27590720000012</v>
+      </c>
+      <c r="K111" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L111">
         <v>65</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -4849,11 +6645,27 @@
       <c r="G112" s="1">
         <v>397.88400000000001</v>
       </c>
-      <c r="H112">
+      <c r="H112" s="1">
+        <f t="shared" si="4"/>
+        <v>449.60891999999996</v>
+      </c>
+      <c r="I112" s="1">
+        <f t="shared" si="5"/>
+        <v>636.61440000000005</v>
+      </c>
+      <c r="J112" s="1">
+        <f t="shared" si="6"/>
+        <v>585.68524800000012</v>
+      </c>
+      <c r="K112" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L112">
         <v>64</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>36</v>
       </c>
@@ -4875,11 +6687,27 @@
       <c r="G113" s="1">
         <v>589.64789999999994</v>
       </c>
-      <c r="H113">
+      <c r="H113" s="1">
+        <f t="shared" si="4"/>
+        <v>666.30212699999981</v>
+      </c>
+      <c r="I113" s="1">
+        <f t="shared" si="5"/>
+        <v>943.4366399999999</v>
+      </c>
+      <c r="J113" s="1">
+        <f t="shared" si="6"/>
+        <v>867.9617088</v>
+      </c>
+      <c r="K113" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L113">
         <v>64</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -4901,11 +6729,27 @@
       <c r="G114" s="1">
         <v>549.35895000000005</v>
       </c>
-      <c r="H114">
+      <c r="H114" s="1">
+        <f t="shared" si="4"/>
+        <v>620.77561349999996</v>
+      </c>
+      <c r="I114" s="1">
+        <f t="shared" si="5"/>
+        <v>878.97432000000015</v>
+      </c>
+      <c r="J114" s="1">
+        <f t="shared" si="6"/>
+        <v>808.65637440000012</v>
+      </c>
+      <c r="K114" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L114">
         <v>63</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>72</v>
       </c>
@@ -4927,11 +6771,27 @@
       <c r="G115" s="1">
         <v>314.38799999999998</v>
       </c>
-      <c r="H115">
+      <c r="H115" s="1">
+        <f t="shared" si="4"/>
+        <v>355.25843999999995</v>
+      </c>
+      <c r="I115" s="1">
+        <f t="shared" si="5"/>
+        <v>503.02080000000001</v>
+      </c>
+      <c r="J115" s="1">
+        <f t="shared" si="6"/>
+        <v>462.77913600000005</v>
+      </c>
+      <c r="K115" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L115">
         <v>62</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>201</v>
       </c>
@@ -4953,11 +6813,27 @@
       <c r="G116" s="1">
         <v>354.99644999999998</v>
       </c>
-      <c r="H116">
+      <c r="H116" s="1">
+        <f t="shared" si="4"/>
+        <v>401.14598849999993</v>
+      </c>
+      <c r="I116" s="1">
+        <f t="shared" si="5"/>
+        <v>567.99432000000002</v>
+      </c>
+      <c r="J116" s="1">
+        <f t="shared" si="6"/>
+        <v>522.55477440000004</v>
+      </c>
+      <c r="K116" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L116">
         <v>62</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>253</v>
       </c>
@@ -4979,11 +6855,27 @@
       <c r="G117" s="1">
         <v>220.12484999999998</v>
       </c>
-      <c r="H117">
+      <c r="H117" s="1">
+        <f t="shared" si="4"/>
+        <v>248.74108049999995</v>
+      </c>
+      <c r="I117" s="1">
+        <f t="shared" si="5"/>
+        <v>352.19975999999997</v>
+      </c>
+      <c r="J117" s="1">
+        <f t="shared" si="6"/>
+        <v>324.02377919999998</v>
+      </c>
+      <c r="K117" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L117">
         <v>62</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>262</v>
       </c>
@@ -5005,11 +6897,27 @@
       <c r="G118" s="1">
         <v>268.85924999999997</v>
       </c>
-      <c r="H118">
+      <c r="H118" s="1">
+        <f t="shared" si="4"/>
+        <v>303.81095249999993</v>
+      </c>
+      <c r="I118" s="1">
+        <f t="shared" si="5"/>
+        <v>430.1748</v>
+      </c>
+      <c r="J118" s="1">
+        <f t="shared" si="6"/>
+        <v>395.76081600000003</v>
+      </c>
+      <c r="K118" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L118">
         <v>62</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>287</v>
       </c>
@@ -5031,11 +6939,27 @@
       <c r="G119" s="1">
         <v>657.81854999999996</v>
       </c>
-      <c r="H119">
+      <c r="H119" s="1">
+        <f t="shared" si="4"/>
+        <v>743.33496149999985</v>
+      </c>
+      <c r="I119" s="1">
+        <f t="shared" si="5"/>
+        <v>1052.5096799999999</v>
+      </c>
+      <c r="J119" s="1">
+        <f t="shared" si="6"/>
+        <v>968.30890559999989</v>
+      </c>
+      <c r="K119" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L119">
         <v>62</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>288</v>
       </c>
@@ -5057,11 +6981,27 @@
       <c r="G120" s="1">
         <v>1588.4368499999998</v>
       </c>
-      <c r="H120">
+      <c r="H120" s="1">
+        <f t="shared" si="4"/>
+        <v>1794.9336404999997</v>
+      </c>
+      <c r="I120" s="1">
+        <f t="shared" si="5"/>
+        <v>2541.4989599999999</v>
+      </c>
+      <c r="J120" s="1">
+        <f t="shared" si="6"/>
+        <v>2338.1790431999998</v>
+      </c>
+      <c r="K120" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L120">
         <v>61</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>341</v>
       </c>
@@ -5083,11 +7023,27 @@
       <c r="G121" s="1">
         <v>174.0849</v>
       </c>
-      <c r="H121">
+      <c r="H121" s="1">
+        <f t="shared" si="4"/>
+        <v>196.715937</v>
+      </c>
+      <c r="I121" s="1">
+        <f t="shared" si="5"/>
+        <v>278.53584000000001</v>
+      </c>
+      <c r="J121" s="1">
+        <f t="shared" si="6"/>
+        <v>256.25297280000001</v>
+      </c>
+      <c r="K121" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L121">
         <v>61</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>119</v>
       </c>
@@ -5109,11 +7065,27 @@
       <c r="G122" s="1">
         <v>155.25569999999999</v>
       </c>
-      <c r="H122">
+      <c r="H122" s="1">
+        <f t="shared" si="4"/>
+        <v>175.43894099999997</v>
+      </c>
+      <c r="I122" s="1">
+        <f t="shared" si="5"/>
+        <v>248.40912</v>
+      </c>
+      <c r="J122" s="1">
+        <f t="shared" si="6"/>
+        <v>228.53639040000002</v>
+      </c>
+      <c r="K122" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L122">
         <v>60</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>407</v>
       </c>
@@ -5135,11 +7107,27 @@
       <c r="G123" s="1">
         <v>263.72594999999995</v>
       </c>
-      <c r="H123">
+      <c r="H123" s="1">
+        <f t="shared" si="4"/>
+        <v>298.01032349999991</v>
+      </c>
+      <c r="I123" s="1">
+        <f t="shared" si="5"/>
+        <v>421.96151999999995</v>
+      </c>
+      <c r="J123" s="1">
+        <f t="shared" si="6"/>
+        <v>388.20459839999995</v>
+      </c>
+      <c r="K123" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L123">
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>305</v>
       </c>
@@ -5161,11 +7149,27 @@
       <c r="G124" s="1">
         <v>244.63049999999998</v>
       </c>
-      <c r="H124">
+      <c r="H124" s="1">
+        <f t="shared" si="4"/>
+        <v>276.43246499999998</v>
+      </c>
+      <c r="I124" s="1">
+        <f t="shared" si="5"/>
+        <v>391.40879999999999</v>
+      </c>
+      <c r="J124" s="1">
+        <f t="shared" si="6"/>
+        <v>360.09609599999999</v>
+      </c>
+      <c r="K124" s="6">
+        <f t="shared" si="7"/>
+        <v>1.472</v>
+      </c>
+      <c r="L124">
         <v>58</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>383</v>
       </c>
@@ -5187,11 +7191,27 @@
       <c r="G125" s="1">
         <v>306.5283</v>
       </c>
-      <c r="H125">
+      <c r="H125" s="1">
+        <f t="shared" si="4"/>
+        <v>346.37697899999995</v>
+      </c>
+      <c r="I125" s="1">
+        <f t="shared" si="5"/>
+        <v>490.44528000000003</v>
+      </c>
+      <c r="J125" s="1">
+        <f t="shared" si="6"/>
+        <v>451.20965760000007</v>
+      </c>
+      <c r="K125" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L125">
         <v>58</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>94</v>
       </c>
@@ -5213,11 +7233,27 @@
       <c r="G126" s="1">
         <v>311.29950000000002</v>
       </c>
-      <c r="H126">
+      <c r="H126" s="1">
+        <f t="shared" si="4"/>
+        <v>351.76843500000001</v>
+      </c>
+      <c r="I126" s="1">
+        <f t="shared" si="5"/>
+        <v>498.07920000000007</v>
+      </c>
+      <c r="J126" s="1">
+        <f t="shared" si="6"/>
+        <v>458.23286400000006</v>
+      </c>
+      <c r="K126" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L126">
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>286</v>
       </c>
@@ -5239,11 +7275,27 @@
       <c r="G127" s="1">
         <v>1495.3771499999998</v>
       </c>
-      <c r="H127">
+      <c r="H127" s="1">
+        <f t="shared" si="4"/>
+        <v>1689.7761794999997</v>
+      </c>
+      <c r="I127" s="1">
+        <f t="shared" si="5"/>
+        <v>2392.6034399999999</v>
+      </c>
+      <c r="J127" s="1">
+        <f t="shared" si="6"/>
+        <v>2201.1951647999999</v>
+      </c>
+      <c r="K127" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L127">
         <v>56</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>146</v>
       </c>
@@ -5265,11 +7317,27 @@
       <c r="G128" s="1">
         <v>266.67599999999999</v>
       </c>
-      <c r="H128">
+      <c r="H128" s="1">
+        <f t="shared" si="4"/>
+        <v>301.34387999999996</v>
+      </c>
+      <c r="I128" s="1">
+        <f t="shared" si="5"/>
+        <v>426.6816</v>
+      </c>
+      <c r="J128" s="1">
+        <f t="shared" si="6"/>
+        <v>392.54707200000001</v>
+      </c>
+      <c r="K128" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L128">
         <v>55</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>355</v>
       </c>
@@ -5291,11 +7359,27 @@
       <c r="G129" s="1">
         <v>443.60444999999993</v>
       </c>
-      <c r="H129">
+      <c r="H129" s="1">
+        <f t="shared" si="4"/>
+        <v>501.2730284999999</v>
+      </c>
+      <c r="I129" s="1">
+        <f t="shared" si="5"/>
+        <v>709.76711999999998</v>
+      </c>
+      <c r="J129" s="1">
+        <f t="shared" si="6"/>
+        <v>652.98575040000003</v>
+      </c>
+      <c r="K129" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L129">
         <v>55</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>83</v>
       </c>
@@ -5317,11 +7401,27 @@
       <c r="G130" s="1">
         <v>272.87430000000001</v>
       </c>
-      <c r="H130">
+      <c r="H130" s="1">
+        <f t="shared" si="4"/>
+        <v>308.347959</v>
+      </c>
+      <c r="I130" s="1">
+        <f t="shared" si="5"/>
+        <v>436.59888000000001</v>
+      </c>
+      <c r="J130" s="1">
+        <f t="shared" si="6"/>
+        <v>401.67096960000003</v>
+      </c>
+      <c r="K130" s="6">
+        <f t="shared" si="7"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L130">
         <v>54</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>130</v>
       </c>
@@ -5343,11 +7443,27 @@
       <c r="G131" s="1">
         <v>284.98334999999997</v>
       </c>
-      <c r="H131">
+      <c r="H131" s="1">
+        <f t="shared" ref="H131:H194" si="8">G131*1.13</f>
+        <v>322.03118549999994</v>
+      </c>
+      <c r="I131" s="1">
+        <f t="shared" ref="I131:I194" si="9">G131*1.6</f>
+        <v>455.97335999999996</v>
+      </c>
+      <c r="J131" s="1">
+        <f t="shared" ref="J131:J194" si="10">I131*0.92</f>
+        <v>419.4954912</v>
+      </c>
+      <c r="K131" s="6">
+        <f t="shared" ref="K131:K194" si="11">J131/G131</f>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L131">
         <v>50</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>241</v>
       </c>
@@ -5369,11 +7485,27 @@
       <c r="G132" s="1">
         <v>954.59145000000001</v>
       </c>
-      <c r="H132">
+      <c r="H132" s="1">
+        <f t="shared" si="8"/>
+        <v>1078.6883384999999</v>
+      </c>
+      <c r="I132" s="1">
+        <f t="shared" si="9"/>
+        <v>1527.3463200000001</v>
+      </c>
+      <c r="J132" s="1">
+        <f t="shared" si="10"/>
+        <v>1405.1586144000003</v>
+      </c>
+      <c r="K132" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L132">
         <v>50</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>186</v>
       </c>
@@ -5395,11 +7527,27 @@
       <c r="G133" s="1">
         <v>244.33229999999998</v>
       </c>
-      <c r="H133">
+      <c r="H133" s="1">
+        <f t="shared" si="8"/>
+        <v>276.09549899999996</v>
+      </c>
+      <c r="I133" s="1">
+        <f t="shared" si="9"/>
+        <v>390.93167999999997</v>
+      </c>
+      <c r="J133" s="1">
+        <f t="shared" si="10"/>
+        <v>359.65714559999998</v>
+      </c>
+      <c r="K133" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L133">
         <v>49</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>182</v>
       </c>
@@ -5421,11 +7569,27 @@
       <c r="G134" s="1">
         <v>339.50069999999994</v>
       </c>
-      <c r="H134">
+      <c r="H134" s="1">
+        <f t="shared" si="8"/>
+        <v>383.63579099999987</v>
+      </c>
+      <c r="I134" s="1">
+        <f t="shared" si="9"/>
+        <v>543.20111999999995</v>
+      </c>
+      <c r="J134" s="1">
+        <f t="shared" si="10"/>
+        <v>499.74503039999996</v>
+      </c>
+      <c r="K134" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L134">
         <v>48</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>198</v>
       </c>
@@ -5447,11 +7611,27 @@
       <c r="G135" s="1">
         <v>253.6617</v>
       </c>
-      <c r="H135">
+      <c r="H135" s="1">
+        <f t="shared" si="8"/>
+        <v>286.63772099999994</v>
+      </c>
+      <c r="I135" s="1">
+        <f t="shared" si="9"/>
+        <v>405.85872000000001</v>
+      </c>
+      <c r="J135" s="1">
+        <f t="shared" si="10"/>
+        <v>373.39002240000002</v>
+      </c>
+      <c r="K135" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L135">
         <v>48</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>230</v>
       </c>
@@ -5473,11 +7653,27 @@
       <c r="G136" s="1">
         <v>165.36255</v>
       </c>
-      <c r="H136">
+      <c r="H136" s="1">
+        <f t="shared" si="8"/>
+        <v>186.85968149999999</v>
+      </c>
+      <c r="I136" s="1">
+        <f t="shared" si="9"/>
+        <v>264.58008000000001</v>
+      </c>
+      <c r="J136" s="1">
+        <f t="shared" si="10"/>
+        <v>243.41367360000001</v>
+      </c>
+      <c r="K136" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L136">
         <v>47</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>342</v>
       </c>
@@ -5499,11 +7695,27 @@
       <c r="G137" s="1">
         <v>358.53224999999998</v>
       </c>
-      <c r="H137">
+      <c r="H137" s="1">
+        <f t="shared" si="8"/>
+        <v>405.14144249999993</v>
+      </c>
+      <c r="I137" s="1">
+        <f t="shared" si="9"/>
+        <v>573.65160000000003</v>
+      </c>
+      <c r="J137" s="1">
+        <f t="shared" si="10"/>
+        <v>527.75947200000007</v>
+      </c>
+      <c r="K137" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L137">
         <v>47</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>178</v>
       </c>
@@ -5525,11 +7737,27 @@
       <c r="G138" s="1">
         <v>1419.40005</v>
       </c>
-      <c r="H138">
+      <c r="H138" s="1">
+        <f t="shared" si="8"/>
+        <v>1603.9220564999998</v>
+      </c>
+      <c r="I138" s="1">
+        <f t="shared" si="9"/>
+        <v>2271.0400800000002</v>
+      </c>
+      <c r="J138" s="1">
+        <f t="shared" si="10"/>
+        <v>2089.3568736000002</v>
+      </c>
+      <c r="K138" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L138">
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>203</v>
       </c>
@@ -5551,11 +7779,27 @@
       <c r="G139" s="1">
         <v>326.17754999999994</v>
       </c>
-      <c r="H139">
+      <c r="H139" s="1">
+        <f t="shared" si="8"/>
+        <v>368.58063149999992</v>
+      </c>
+      <c r="I139" s="1">
+        <f t="shared" si="9"/>
+        <v>521.88407999999993</v>
+      </c>
+      <c r="J139" s="1">
+        <f t="shared" si="10"/>
+        <v>480.13335359999996</v>
+      </c>
+      <c r="K139" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L139">
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>284</v>
       </c>
@@ -5577,11 +7821,27 @@
       <c r="G140" s="1">
         <v>1588.4368499999998</v>
       </c>
-      <c r="H140">
+      <c r="H140" s="1">
+        <f t="shared" si="8"/>
+        <v>1794.9336404999997</v>
+      </c>
+      <c r="I140" s="1">
+        <f t="shared" si="9"/>
+        <v>2541.4989599999999</v>
+      </c>
+      <c r="J140" s="1">
+        <f t="shared" si="10"/>
+        <v>2338.1790431999998</v>
+      </c>
+      <c r="K140" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L140">
         <v>46</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>249</v>
       </c>
@@ -5603,11 +7863,27 @@
       <c r="G141" s="1">
         <v>528.70859999999993</v>
       </c>
-      <c r="H141">
+      <c r="H141" s="1">
+        <f t="shared" si="8"/>
+        <v>597.44071799999983</v>
+      </c>
+      <c r="I141" s="1">
+        <f t="shared" si="9"/>
+        <v>845.93375999999989</v>
+      </c>
+      <c r="J141" s="1">
+        <f t="shared" si="10"/>
+        <v>778.25905919999991</v>
+      </c>
+      <c r="K141" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L141">
         <v>45</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>348</v>
       </c>
@@ -5629,11 +7905,27 @@
       <c r="G142" s="1">
         <v>316.31564999999995</v>
       </c>
-      <c r="H142">
+      <c r="H142" s="1">
+        <f t="shared" si="8"/>
+        <v>357.4366844999999</v>
+      </c>
+      <c r="I142" s="1">
+        <f t="shared" si="9"/>
+        <v>506.10503999999992</v>
+      </c>
+      <c r="J142" s="1">
+        <f t="shared" si="10"/>
+        <v>465.61663679999992</v>
+      </c>
+      <c r="K142" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L142">
         <v>45</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>356</v>
       </c>
@@ -5655,11 +7947,27 @@
       <c r="G143" s="1">
         <v>521.94584999999995</v>
       </c>
-      <c r="H143">
+      <c r="H143" s="1">
+        <f t="shared" si="8"/>
+        <v>589.79881049999995</v>
+      </c>
+      <c r="I143" s="1">
+        <f t="shared" si="9"/>
+        <v>835.11335999999994</v>
+      </c>
+      <c r="J143" s="1">
+        <f t="shared" si="10"/>
+        <v>768.30429119999997</v>
+      </c>
+      <c r="K143" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L143">
         <v>44</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -5681,11 +7989,27 @@
       <c r="G144" s="1">
         <v>266.67599999999999</v>
       </c>
-      <c r="H144">
+      <c r="H144" s="1">
+        <f t="shared" si="8"/>
+        <v>301.34387999999996</v>
+      </c>
+      <c r="I144" s="1">
+        <f t="shared" si="9"/>
+        <v>426.6816</v>
+      </c>
+      <c r="J144" s="1">
+        <f t="shared" si="10"/>
+        <v>392.54707200000001</v>
+      </c>
+      <c r="K144" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L144">
         <v>43</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>243</v>
       </c>
@@ -5707,11 +8031,27 @@
       <c r="G145" s="1">
         <v>1047.5553</v>
       </c>
-      <c r="H145">
+      <c r="H145" s="1">
+        <f t="shared" si="8"/>
+        <v>1183.7374889999999</v>
+      </c>
+      <c r="I145" s="1">
+        <f t="shared" si="9"/>
+        <v>1676.0884800000001</v>
+      </c>
+      <c r="J145" s="1">
+        <f t="shared" si="10"/>
+        <v>1542.0014016000002</v>
+      </c>
+      <c r="K145" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L145">
         <v>43</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>251</v>
       </c>
@@ -5733,11 +8073,27 @@
       <c r="G146" s="1">
         <v>749.34465</v>
       </c>
-      <c r="H146">
+      <c r="H146" s="1">
+        <f t="shared" si="8"/>
+        <v>846.75945449999995</v>
+      </c>
+      <c r="I146" s="1">
+        <f t="shared" si="9"/>
+        <v>1198.95144</v>
+      </c>
+      <c r="J146" s="1">
+        <f t="shared" si="10"/>
+        <v>1103.0353248000001</v>
+      </c>
+      <c r="K146" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L146">
         <v>43</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>368</v>
       </c>
@@ -5759,11 +8115,27 @@
       <c r="G147" s="1">
         <v>186.9288</v>
       </c>
-      <c r="H147">
+      <c r="H147" s="1">
+        <f t="shared" si="8"/>
+        <v>211.22954399999998</v>
+      </c>
+      <c r="I147" s="1">
+        <f t="shared" si="9"/>
+        <v>299.08607999999998</v>
+      </c>
+      <c r="J147" s="1">
+        <f t="shared" si="10"/>
+        <v>275.15919359999998</v>
+      </c>
+      <c r="K147" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L147">
         <v>43</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>115</v>
       </c>
@@ -5785,11 +8157,27 @@
       <c r="G148" s="1">
         <v>541.81875000000002</v>
       </c>
-      <c r="H148">
+      <c r="H148" s="1">
+        <f t="shared" si="8"/>
+        <v>612.25518749999992</v>
+      </c>
+      <c r="I148" s="1">
+        <f t="shared" si="9"/>
+        <v>866.91000000000008</v>
+      </c>
+      <c r="J148" s="1">
+        <f t="shared" si="10"/>
+        <v>797.55720000000008</v>
+      </c>
+      <c r="K148" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L148">
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>167</v>
       </c>
@@ -5811,11 +8199,27 @@
       <c r="G149" s="1">
         <v>139.63215</v>
       </c>
-      <c r="H149">
+      <c r="H149" s="1">
+        <f t="shared" si="8"/>
+        <v>157.78432949999998</v>
+      </c>
+      <c r="I149" s="1">
+        <f t="shared" si="9"/>
+        <v>223.41144</v>
+      </c>
+      <c r="J149" s="1">
+        <f t="shared" si="10"/>
+        <v>205.5385248</v>
+      </c>
+      <c r="K149" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L149">
         <v>40</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>242</v>
       </c>
@@ -5837,11 +8241,27 @@
       <c r="G150" s="1">
         <v>991.78125</v>
       </c>
-      <c r="H150">
+      <c r="H150" s="1">
+        <f t="shared" si="8"/>
+        <v>1120.7128124999999</v>
+      </c>
+      <c r="I150" s="1">
+        <f t="shared" si="9"/>
+        <v>1586.8500000000001</v>
+      </c>
+      <c r="J150" s="1">
+        <f t="shared" si="10"/>
+        <v>1459.9020000000003</v>
+      </c>
+      <c r="K150" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L150">
         <v>40</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>38</v>
       </c>
@@ -5863,11 +8283,27 @@
       <c r="G151" s="1">
         <v>1080.79395</v>
       </c>
-      <c r="H151">
+      <c r="H151" s="1">
+        <f t="shared" si="8"/>
+        <v>1221.2971634999999</v>
+      </c>
+      <c r="I151" s="1">
+        <f t="shared" si="9"/>
+        <v>1729.2703200000001</v>
+      </c>
+      <c r="J151" s="1">
+        <f t="shared" si="10"/>
+        <v>1590.9286944</v>
+      </c>
+      <c r="K151" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L151">
         <v>39</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>85</v>
       </c>
@@ -5889,11 +8325,27 @@
       <c r="G152" s="1">
         <v>358.53224999999998</v>
       </c>
-      <c r="H152">
+      <c r="H152" s="1">
+        <f t="shared" si="8"/>
+        <v>405.14144249999993</v>
+      </c>
+      <c r="I152" s="1">
+        <f t="shared" si="9"/>
+        <v>573.65160000000003</v>
+      </c>
+      <c r="J152" s="1">
+        <f t="shared" si="10"/>
+        <v>527.75947200000007</v>
+      </c>
+      <c r="K152" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L152">
         <v>39</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>245</v>
       </c>
@@ -5915,11 +8367,27 @@
       <c r="G153" s="1">
         <v>843.04335000000003</v>
       </c>
-      <c r="H153">
+      <c r="H153" s="1">
+        <f t="shared" si="8"/>
+        <v>952.63898549999999</v>
+      </c>
+      <c r="I153" s="1">
+        <f t="shared" si="9"/>
+        <v>1348.8693600000001</v>
+      </c>
+      <c r="J153" s="1">
+        <f t="shared" si="10"/>
+        <v>1240.9598112000001</v>
+      </c>
+      <c r="K153" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L153">
         <v>39</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>396</v>
       </c>
@@ -5941,11 +8409,27 @@
       <c r="G154" s="1">
         <v>600.26594999999998</v>
       </c>
-      <c r="H154">
+      <c r="H154" s="1">
+        <f t="shared" si="8"/>
+        <v>678.30052349999994</v>
+      </c>
+      <c r="I154" s="1">
+        <f t="shared" si="9"/>
+        <v>960.42552000000001</v>
+      </c>
+      <c r="J154" s="1">
+        <f t="shared" si="10"/>
+        <v>883.59147840000003</v>
+      </c>
+      <c r="K154" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L154">
         <v>39</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>240</v>
       </c>
@@ -5967,11 +8451,27 @@
       <c r="G155" s="1">
         <v>601.34159999999997</v>
       </c>
-      <c r="H155">
+      <c r="H155" s="1">
+        <f t="shared" si="8"/>
+        <v>679.51600799999994</v>
+      </c>
+      <c r="I155" s="1">
+        <f t="shared" si="9"/>
+        <v>962.14656000000002</v>
+      </c>
+      <c r="J155" s="1">
+        <f t="shared" si="10"/>
+        <v>885.17483520000008</v>
+      </c>
+      <c r="K155" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L155">
         <v>38</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>120</v>
       </c>
@@ -5993,11 +8493,27 @@
       <c r="G156" s="1">
         <v>129.37620000000001</v>
       </c>
-      <c r="H156">
+      <c r="H156" s="1">
+        <f t="shared" si="8"/>
+        <v>146.19510600000001</v>
+      </c>
+      <c r="I156" s="1">
+        <f t="shared" si="9"/>
+        <v>207.00192000000004</v>
+      </c>
+      <c r="J156" s="1">
+        <f t="shared" si="10"/>
+        <v>190.44176640000003</v>
+      </c>
+      <c r="K156" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L156">
         <v>37</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>353</v>
       </c>
@@ -6019,11 +8535,27 @@
       <c r="G157" s="1">
         <v>521.94584999999995</v>
       </c>
-      <c r="H157">
+      <c r="H157" s="1">
+        <f t="shared" si="8"/>
+        <v>589.79881049999995</v>
+      </c>
+      <c r="I157" s="1">
+        <f t="shared" si="9"/>
+        <v>835.11335999999994</v>
+      </c>
+      <c r="J157" s="1">
+        <f t="shared" si="10"/>
+        <v>768.30429119999997</v>
+      </c>
+      <c r="K157" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L157">
         <v>37</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>99</v>
       </c>
@@ -6045,11 +8577,27 @@
       <c r="G158" s="1">
         <v>186.7371</v>
       </c>
-      <c r="H158">
+      <c r="H158" s="1">
+        <f t="shared" si="8"/>
+        <v>211.01292299999997</v>
+      </c>
+      <c r="I158" s="1">
+        <f t="shared" si="9"/>
+        <v>298.77936</v>
+      </c>
+      <c r="J158" s="1">
+        <f t="shared" si="10"/>
+        <v>274.87701120000003</v>
+      </c>
+      <c r="K158" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L158">
         <v>36</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>208</v>
       </c>
@@ -6071,11 +8619,27 @@
       <c r="G159" s="1">
         <v>530.44454999999994</v>
       </c>
-      <c r="H159">
+      <c r="H159" s="1">
+        <f t="shared" si="8"/>
+        <v>599.40234149999992</v>
+      </c>
+      <c r="I159" s="1">
+        <f t="shared" si="9"/>
+        <v>848.71127999999999</v>
+      </c>
+      <c r="J159" s="1">
+        <f t="shared" si="10"/>
+        <v>780.81437760000006</v>
+      </c>
+      <c r="K159" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L159">
         <v>34</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>311</v>
       </c>
@@ -6097,11 +8661,27 @@
       <c r="G160" s="1">
         <v>994.8377999999999</v>
       </c>
-      <c r="H160">
+      <c r="H160" s="1">
+        <f t="shared" si="8"/>
+        <v>1124.1667139999997</v>
+      </c>
+      <c r="I160" s="1">
+        <f t="shared" si="9"/>
+        <v>1591.7404799999999</v>
+      </c>
+      <c r="J160" s="1">
+        <f t="shared" si="10"/>
+        <v>1464.4012416</v>
+      </c>
+      <c r="K160" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L160">
         <v>34</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>344</v>
       </c>
@@ -6123,11 +8703,27 @@
       <c r="G161" s="1">
         <v>386.77605</v>
       </c>
-      <c r="H161">
+      <c r="H161" s="1">
+        <f t="shared" si="8"/>
+        <v>437.05693649999995</v>
+      </c>
+      <c r="I161" s="1">
+        <f t="shared" si="9"/>
+        <v>618.84168</v>
+      </c>
+      <c r="J161" s="1">
+        <f t="shared" si="10"/>
+        <v>569.33434560000001</v>
+      </c>
+      <c r="K161" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L161">
         <v>34</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>213</v>
       </c>
@@ -6149,11 +8745,27 @@
       <c r="G162" s="1">
         <v>4886.8377</v>
       </c>
-      <c r="H162">
+      <c r="H162" s="1">
+        <f t="shared" si="8"/>
+        <v>5522.1266009999999</v>
+      </c>
+      <c r="I162" s="1">
+        <f t="shared" si="9"/>
+        <v>7818.9403200000006</v>
+      </c>
+      <c r="J162" s="1">
+        <f t="shared" si="10"/>
+        <v>7193.4250944000005</v>
+      </c>
+      <c r="K162" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L162">
         <v>33</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>269</v>
       </c>
@@ -6175,11 +8787,27 @@
       <c r="G163" s="1">
         <v>3057.1250999999997</v>
       </c>
-      <c r="H163">
+      <c r="H163" s="1">
+        <f t="shared" si="8"/>
+        <v>3454.5513629999996</v>
+      </c>
+      <c r="I163" s="1">
+        <f t="shared" si="9"/>
+        <v>4891.4001600000001</v>
+      </c>
+      <c r="J163" s="1">
+        <f t="shared" si="10"/>
+        <v>4500.0881472000001</v>
+      </c>
+      <c r="K163" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L163">
         <v>33</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>351</v>
       </c>
@@ -6201,11 +8829,27 @@
       <c r="G164" s="1">
         <v>521.94584999999995</v>
       </c>
-      <c r="H164">
+      <c r="H164" s="1">
+        <f t="shared" si="8"/>
+        <v>589.79881049999995</v>
+      </c>
+      <c r="I164" s="1">
+        <f t="shared" si="9"/>
+        <v>835.11335999999994</v>
+      </c>
+      <c r="J164" s="1">
+        <f t="shared" si="10"/>
+        <v>768.30429119999997</v>
+      </c>
+      <c r="K164" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L164">
         <v>33</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>358</v>
       </c>
@@ -6227,11 +8871,27 @@
       <c r="G165" s="1">
         <v>698.18205</v>
       </c>
-      <c r="H165">
+      <c r="H165" s="1">
+        <f t="shared" si="8"/>
+        <v>788.94571649999989</v>
+      </c>
+      <c r="I165" s="1">
+        <f t="shared" si="9"/>
+        <v>1117.0912800000001</v>
+      </c>
+      <c r="J165" s="1">
+        <f t="shared" si="10"/>
+        <v>1027.7239776000001</v>
+      </c>
+      <c r="K165" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L165">
         <v>33</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>234</v>
       </c>
@@ -6253,11 +8913,27 @@
       <c r="G166" s="1">
         <v>192.15795</v>
       </c>
-      <c r="H166">
+      <c r="H166" s="1">
+        <f t="shared" si="8"/>
+        <v>217.13848349999998</v>
+      </c>
+      <c r="I166" s="1">
+        <f t="shared" si="9"/>
+        <v>307.45272</v>
+      </c>
+      <c r="J166" s="1">
+        <f t="shared" si="10"/>
+        <v>282.85650240000001</v>
+      </c>
+      <c r="K166" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L166">
         <v>32</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>361</v>
       </c>
@@ -6279,11 +8955,27 @@
       <c r="G167" s="1">
         <v>215.48145</v>
       </c>
-      <c r="H167">
+      <c r="H167" s="1">
+        <f t="shared" si="8"/>
+        <v>243.49403849999996</v>
+      </c>
+      <c r="I167" s="1">
+        <f t="shared" si="9"/>
+        <v>344.77032000000003</v>
+      </c>
+      <c r="J167" s="1">
+        <f t="shared" si="10"/>
+        <v>317.18869440000003</v>
+      </c>
+      <c r="K167" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L167">
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>70</v>
       </c>
@@ -6305,11 +8997,27 @@
       <c r="G168" s="1">
         <v>350.19329999999997</v>
       </c>
-      <c r="H168">
+      <c r="H168" s="1">
+        <f t="shared" si="8"/>
+        <v>395.7184289999999</v>
+      </c>
+      <c r="I168" s="1">
+        <f t="shared" si="9"/>
+        <v>560.30927999999994</v>
+      </c>
+      <c r="J168" s="1">
+        <f t="shared" si="10"/>
+        <v>515.48453759999995</v>
+      </c>
+      <c r="K168" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L168">
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>79</v>
       </c>
@@ -6331,11 +9039,27 @@
       <c r="G169" s="1">
         <v>358.53224999999998</v>
       </c>
-      <c r="H169">
+      <c r="H169" s="1">
+        <f t="shared" si="8"/>
+        <v>405.14144249999993</v>
+      </c>
+      <c r="I169" s="1">
+        <f t="shared" si="9"/>
+        <v>573.65160000000003</v>
+      </c>
+      <c r="J169" s="1">
+        <f t="shared" si="10"/>
+        <v>527.75947200000007</v>
+      </c>
+      <c r="K169" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L169">
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>179</v>
       </c>
@@ -6357,11 +9081,27 @@
       <c r="G170" s="1">
         <v>1809.8290499999998</v>
       </c>
-      <c r="H170">
+      <c r="H170" s="1">
+        <f t="shared" si="8"/>
+        <v>2045.1068264999997</v>
+      </c>
+      <c r="I170" s="1">
+        <f t="shared" si="9"/>
+        <v>2895.7264799999998</v>
+      </c>
+      <c r="J170" s="1">
+        <f t="shared" si="10"/>
+        <v>2664.0683616000001</v>
+      </c>
+      <c r="K170" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L170">
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>180</v>
       </c>
@@ -6383,11 +9123,27 @@
       <c r="G171" s="1">
         <v>1140.5085000000001</v>
       </c>
-      <c r="H171">
+      <c r="H171" s="1">
+        <f t="shared" si="8"/>
+        <v>1288.7746050000001</v>
+      </c>
+      <c r="I171" s="1">
+        <f t="shared" si="9"/>
+        <v>1824.8136000000004</v>
+      </c>
+      <c r="J171" s="1">
+        <f t="shared" si="10"/>
+        <v>1678.8285120000005</v>
+      </c>
+      <c r="K171" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L171">
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>211</v>
       </c>
@@ -6409,11 +9165,27 @@
       <c r="G172" s="1">
         <v>786.82199999999989</v>
       </c>
-      <c r="H172">
+      <c r="H172" s="1">
+        <f t="shared" si="8"/>
+        <v>889.10885999999982</v>
+      </c>
+      <c r="I172" s="1">
+        <f t="shared" si="9"/>
+        <v>1258.9151999999999</v>
+      </c>
+      <c r="J172" s="1">
+        <f t="shared" si="10"/>
+        <v>1158.201984</v>
+      </c>
+      <c r="K172" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L172">
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>256</v>
       </c>
@@ -6435,11 +9207,27 @@
       <c r="G173" s="1">
         <v>749.34465</v>
       </c>
-      <c r="H173">
+      <c r="H173" s="1">
+        <f t="shared" si="8"/>
+        <v>846.75945449999995</v>
+      </c>
+      <c r="I173" s="1">
+        <f t="shared" si="9"/>
+        <v>1198.95144</v>
+      </c>
+      <c r="J173" s="1">
+        <f t="shared" si="10"/>
+        <v>1103.0353248000001</v>
+      </c>
+      <c r="K173" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L173">
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>281</v>
       </c>
@@ -6461,11 +9249,27 @@
       <c r="G174" s="1">
         <v>657.81854999999996</v>
       </c>
-      <c r="H174">
+      <c r="H174" s="1">
+        <f t="shared" si="8"/>
+        <v>743.33496149999985</v>
+      </c>
+      <c r="I174" s="1">
+        <f t="shared" si="9"/>
+        <v>1052.5096799999999</v>
+      </c>
+      <c r="J174" s="1">
+        <f t="shared" si="10"/>
+        <v>968.30890559999989</v>
+      </c>
+      <c r="K174" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L174">
         <v>30</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>309</v>
       </c>
@@ -6487,11 +9291,27 @@
       <c r="G175" s="1">
         <v>522.10559999999998</v>
       </c>
-      <c r="H175">
+      <c r="H175" s="1">
+        <f t="shared" si="8"/>
+        <v>589.9793279999999</v>
+      </c>
+      <c r="I175" s="1">
+        <f t="shared" si="9"/>
+        <v>835.36896000000002</v>
+      </c>
+      <c r="J175" s="1">
+        <f t="shared" si="10"/>
+        <v>768.53944320000005</v>
+      </c>
+      <c r="K175" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L175">
         <v>29</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>246</v>
       </c>
@@ -6513,11 +9333,27 @@
       <c r="G176" s="1">
         <v>286.19745</v>
       </c>
-      <c r="H176">
+      <c r="H176" s="1">
+        <f t="shared" si="8"/>
+        <v>323.40311849999995</v>
+      </c>
+      <c r="I176" s="1">
+        <f t="shared" si="9"/>
+        <v>457.91592000000003</v>
+      </c>
+      <c r="J176" s="1">
+        <f t="shared" si="10"/>
+        <v>421.28264640000003</v>
+      </c>
+      <c r="K176" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L176">
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>125</v>
       </c>
@@ -6539,11 +9375,27 @@
       <c r="G177" s="1">
         <v>543.38430000000005</v>
       </c>
-      <c r="H177">
+      <c r="H177" s="1">
+        <f t="shared" si="8"/>
+        <v>614.02425900000003</v>
+      </c>
+      <c r="I177" s="1">
+        <f t="shared" si="9"/>
+        <v>869.41488000000015</v>
+      </c>
+      <c r="J177" s="1">
+        <f t="shared" si="10"/>
+        <v>799.8616896000002</v>
+      </c>
+      <c r="K177" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L177">
         <v>27</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>177</v>
       </c>
@@ -6565,11 +9417,27 @@
       <c r="G178" s="1">
         <v>647.81819999999993</v>
       </c>
-      <c r="H178">
+      <c r="H178" s="1">
+        <f t="shared" si="8"/>
+        <v>732.03456599999981</v>
+      </c>
+      <c r="I178" s="1">
+        <f t="shared" si="9"/>
+        <v>1036.5091199999999</v>
+      </c>
+      <c r="J178" s="1">
+        <f t="shared" si="10"/>
+        <v>953.58839039999998</v>
+      </c>
+      <c r="K178" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L178">
         <v>27</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>270</v>
       </c>
@@ -6591,11 +9459,27 @@
       <c r="G179" s="1">
         <v>315.71924999999999</v>
       </c>
-      <c r="H179">
+      <c r="H179" s="1">
+        <f t="shared" si="8"/>
+        <v>356.76275249999998</v>
+      </c>
+      <c r="I179" s="1">
+        <f t="shared" si="9"/>
+        <v>505.1508</v>
+      </c>
+      <c r="J179" s="1">
+        <f t="shared" si="10"/>
+        <v>464.73873600000002</v>
+      </c>
+      <c r="K179" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L179">
         <v>27</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>175</v>
       </c>
@@ -6617,11 +9501,27 @@
       <c r="G180" s="1">
         <v>2683.6615499999998</v>
       </c>
-      <c r="H180">
+      <c r="H180" s="1">
+        <f t="shared" si="8"/>
+        <v>3032.5375514999996</v>
+      </c>
+      <c r="I180" s="1">
+        <f t="shared" si="9"/>
+        <v>4293.8584799999999</v>
+      </c>
+      <c r="J180" s="1">
+        <f t="shared" si="10"/>
+        <v>3950.3498015999999</v>
+      </c>
+      <c r="K180" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L180">
         <v>26</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>204</v>
       </c>
@@ -6643,11 +9543,27 @@
       <c r="G181" s="1">
         <v>380.09849999999994</v>
       </c>
-      <c r="H181">
+      <c r="H181" s="1">
+        <f t="shared" si="8"/>
+        <v>429.51130499999988</v>
+      </c>
+      <c r="I181" s="1">
+        <f t="shared" si="9"/>
+        <v>608.15759999999989</v>
+      </c>
+      <c r="J181" s="1">
+        <f t="shared" si="10"/>
+        <v>559.5049919999999</v>
+      </c>
+      <c r="K181" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L181">
         <v>26</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>278</v>
       </c>
@@ -6669,11 +9585,27 @@
       <c r="G182" s="1">
         <v>170.43195</v>
       </c>
-      <c r="H182">
+      <c r="H182" s="1">
+        <f t="shared" si="8"/>
+        <v>192.58810349999999</v>
+      </c>
+      <c r="I182" s="1">
+        <f t="shared" si="9"/>
+        <v>272.69112000000001</v>
+      </c>
+      <c r="J182" s="1">
+        <f t="shared" si="10"/>
+        <v>250.87583040000001</v>
+      </c>
+      <c r="K182" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L182">
         <v>26</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>395</v>
       </c>
@@ -6695,11 +9627,27 @@
       <c r="G183" s="1">
         <v>187.24829999999997</v>
       </c>
-      <c r="H183">
+      <c r="H183" s="1">
+        <f t="shared" si="8"/>
+        <v>211.59057899999993</v>
+      </c>
+      <c r="I183" s="1">
+        <f t="shared" si="9"/>
+        <v>299.59727999999996</v>
+      </c>
+      <c r="J183" s="1">
+        <f t="shared" si="10"/>
+        <v>275.62949759999998</v>
+      </c>
+      <c r="K183" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L183">
         <v>26</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>59</v>
       </c>
@@ -6721,11 +9669,27 @@
       <c r="G184" s="1">
         <v>719.62049999999999</v>
       </c>
-      <c r="H184">
+      <c r="H184" s="1">
+        <f t="shared" si="8"/>
+        <v>813.17116499999986</v>
+      </c>
+      <c r="I184" s="1">
+        <f t="shared" si="9"/>
+        <v>1151.3928000000001</v>
+      </c>
+      <c r="J184" s="1">
+        <f t="shared" si="10"/>
+        <v>1059.2813760000001</v>
+      </c>
+      <c r="K184" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L184">
         <v>25</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>216</v>
       </c>
@@ -6747,11 +9711,27 @@
       <c r="G185" s="1">
         <v>6398.3922000000002</v>
       </c>
-      <c r="H185">
+      <c r="H185" s="1">
+        <f t="shared" si="8"/>
+        <v>7230.1831859999993</v>
+      </c>
+      <c r="I185" s="1">
+        <f t="shared" si="9"/>
+        <v>10237.427520000001</v>
+      </c>
+      <c r="J185" s="1">
+        <f t="shared" si="10"/>
+        <v>9418.4333184000006</v>
+      </c>
+      <c r="K185" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L185">
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>298</v>
       </c>
@@ -6773,11 +9753,27 @@
       <c r="G186" s="1">
         <v>174.60674999999998</v>
       </c>
-      <c r="H186">
+      <c r="H186" s="1">
+        <f t="shared" si="8"/>
+        <v>197.30562749999996</v>
+      </c>
+      <c r="I186" s="1">
+        <f t="shared" si="9"/>
+        <v>279.37079999999997</v>
+      </c>
+      <c r="J186" s="1">
+        <f t="shared" si="10"/>
+        <v>257.02113600000001</v>
+      </c>
+      <c r="K186" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L186">
         <v>25</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>102</v>
       </c>
@@ -6799,11 +9795,27 @@
       <c r="G187" s="1">
         <v>191.02904999999998</v>
       </c>
-      <c r="H187">
+      <c r="H187" s="1">
+        <f t="shared" si="8"/>
+        <v>215.86282649999995</v>
+      </c>
+      <c r="I187" s="1">
+        <f t="shared" si="9"/>
+        <v>305.64648</v>
+      </c>
+      <c r="J187" s="1">
+        <f t="shared" si="10"/>
+        <v>281.19476159999999</v>
+      </c>
+      <c r="K187" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L187">
         <v>24</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>263</v>
       </c>
@@ -6825,11 +9837,27 @@
       <c r="G188" s="1">
         <v>318.0729</v>
       </c>
-      <c r="H188">
+      <c r="H188" s="1">
+        <f t="shared" si="8"/>
+        <v>359.42237699999998</v>
+      </c>
+      <c r="I188" s="1">
+        <f t="shared" si="9"/>
+        <v>508.91664000000003</v>
+      </c>
+      <c r="J188" s="1">
+        <f t="shared" si="10"/>
+        <v>468.20330880000006</v>
+      </c>
+      <c r="K188" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L188">
         <v>24</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>274</v>
       </c>
@@ -6851,11 +9879,27 @@
       <c r="G189" s="1">
         <v>580.27589999999998</v>
       </c>
-      <c r="H189">
+      <c r="H189" s="1">
+        <f t="shared" si="8"/>
+        <v>655.7117669999999</v>
+      </c>
+      <c r="I189" s="1">
+        <f t="shared" si="9"/>
+        <v>928.44144000000006</v>
+      </c>
+      <c r="J189" s="1">
+        <f t="shared" si="10"/>
+        <v>854.16612480000003</v>
+      </c>
+      <c r="K189" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L189">
         <v>24</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>307</v>
       </c>
@@ -6877,11 +9921,27 @@
       <c r="G190" s="1">
         <v>436.14944999999994</v>
       </c>
-      <c r="H190">
+      <c r="H190" s="1">
+        <f t="shared" si="8"/>
+        <v>492.8488784999999</v>
+      </c>
+      <c r="I190" s="1">
+        <f t="shared" si="9"/>
+        <v>697.83911999999998</v>
+      </c>
+      <c r="J190" s="1">
+        <f t="shared" si="10"/>
+        <v>642.01199040000006</v>
+      </c>
+      <c r="K190" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L190">
         <v>24</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>370</v>
       </c>
@@ -6903,11 +9963,27 @@
       <c r="G191" s="1">
         <v>183.02024999999998</v>
       </c>
-      <c r="H191">
+      <c r="H191" s="1">
+        <f t="shared" si="8"/>
+        <v>206.81288249999994</v>
+      </c>
+      <c r="I191" s="1">
+        <f t="shared" si="9"/>
+        <v>292.83239999999995</v>
+      </c>
+      <c r="J191" s="1">
+        <f t="shared" si="10"/>
+        <v>269.40580799999998</v>
+      </c>
+      <c r="K191" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L191">
         <v>24</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>261</v>
       </c>
@@ -6929,11 +10005,27 @@
       <c r="G192" s="1">
         <v>396.44624999999996</v>
       </c>
-      <c r="H192">
+      <c r="H192" s="1">
+        <f t="shared" si="8"/>
+        <v>447.98426249999994</v>
+      </c>
+      <c r="I192" s="1">
+        <f t="shared" si="9"/>
+        <v>634.31399999999996</v>
+      </c>
+      <c r="J192" s="1">
+        <f t="shared" si="10"/>
+        <v>583.56888000000004</v>
+      </c>
+      <c r="K192" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L192">
         <v>23</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>332</v>
       </c>
@@ -6955,11 +10047,27 @@
       <c r="G193" s="1">
         <v>805.86419999999987</v>
       </c>
-      <c r="H193">
+      <c r="H193" s="1">
+        <f t="shared" si="8"/>
+        <v>910.62654599999973</v>
+      </c>
+      <c r="I193" s="1">
+        <f t="shared" si="9"/>
+        <v>1289.3827199999998</v>
+      </c>
+      <c r="J193" s="1">
+        <f t="shared" si="10"/>
+        <v>1186.2321023999998</v>
+      </c>
+      <c r="K193" s="6">
+        <f t="shared" si="11"/>
+        <v>1.472</v>
+      </c>
+      <c r="L193">
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>27</v>
       </c>
@@ -6981,11 +10089,27 @@
       <c r="G194" s="1">
         <v>397.88400000000001</v>
       </c>
-      <c r="H194">
+      <c r="H194" s="1">
+        <f t="shared" si="8"/>
+        <v>449.60891999999996</v>
+      </c>
+      <c r="I194" s="1">
+        <f t="shared" si="9"/>
+        <v>636.61440000000005</v>
+      </c>
+      <c r="J194" s="1">
+        <f t="shared" si="10"/>
+        <v>585.68524800000012</v>
+      </c>
+      <c r="K194" s="6">
+        <f t="shared" si="11"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L194">
         <v>22</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>46</v>
       </c>
@@ -7007,11 +10131,27 @@
       <c r="G195" s="1">
         <v>658.34039999999993</v>
       </c>
-      <c r="H195">
+      <c r="H195" s="1">
+        <f t="shared" ref="H195:H258" si="12">G195*1.13</f>
+        <v>743.92465199999981</v>
+      </c>
+      <c r="I195" s="1">
+        <f t="shared" ref="I195:I258" si="13">G195*1.6</f>
+        <v>1053.34464</v>
+      </c>
+      <c r="J195" s="1">
+        <f t="shared" ref="J195:J258" si="14">I195*0.92</f>
+        <v>969.07706880000012</v>
+      </c>
+      <c r="K195" s="6">
+        <f t="shared" ref="K195:K258" si="15">J195/G195</f>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L195">
         <v>22</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>52</v>
       </c>
@@ -7033,11 +10173,27 @@
       <c r="G196" s="1">
         <v>954.12284999999997</v>
       </c>
-      <c r="H196">
+      <c r="H196" s="1">
+        <f t="shared" si="12"/>
+        <v>1078.1588204999998</v>
+      </c>
+      <c r="I196" s="1">
+        <f t="shared" si="13"/>
+        <v>1526.59656</v>
+      </c>
+      <c r="J196" s="1">
+        <f t="shared" si="14"/>
+        <v>1404.4688352000001</v>
+      </c>
+      <c r="K196" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L196">
         <v>22</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>82</v>
       </c>
@@ -7059,11 +10215,27 @@
       <c r="G197" s="1">
         <v>280.49969999999996</v>
       </c>
-      <c r="H197">
+      <c r="H197" s="1">
+        <f t="shared" si="12"/>
+        <v>316.96466099999992</v>
+      </c>
+      <c r="I197" s="1">
+        <f t="shared" si="13"/>
+        <v>448.79951999999997</v>
+      </c>
+      <c r="J197" s="1">
+        <f t="shared" si="14"/>
+        <v>412.89555839999997</v>
+      </c>
+      <c r="K197" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L197">
         <v>22</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>51</v>
       </c>
@@ -7085,11 +10257,27 @@
       <c r="G198" s="1">
         <v>812.19029999999998</v>
       </c>
-      <c r="H198">
+      <c r="H198" s="1">
+        <f t="shared" si="12"/>
+        <v>917.77503899999988</v>
+      </c>
+      <c r="I198" s="1">
+        <f t="shared" si="13"/>
+        <v>1299.5044800000001</v>
+      </c>
+      <c r="J198" s="1">
+        <f t="shared" si="14"/>
+        <v>1195.5441216000002</v>
+      </c>
+      <c r="K198" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L198">
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>133</v>
       </c>
@@ -7111,11 +10299,27 @@
       <c r="G199" s="1">
         <v>762.81689999999992</v>
       </c>
-      <c r="H199">
+      <c r="H199" s="1">
+        <f t="shared" si="12"/>
+        <v>861.98309699999982</v>
+      </c>
+      <c r="I199" s="1">
+        <f t="shared" si="13"/>
+        <v>1220.50704</v>
+      </c>
+      <c r="J199" s="1">
+        <f t="shared" si="14"/>
+        <v>1122.8664768000001</v>
+      </c>
+      <c r="K199" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L199">
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>181</v>
       </c>
@@ -7137,11 +10341,27 @@
       <c r="G200" s="1">
         <v>1066.1502</v>
       </c>
-      <c r="H200">
+      <c r="H200" s="1">
+        <f t="shared" si="12"/>
+        <v>1204.749726</v>
+      </c>
+      <c r="I200" s="1">
+        <f t="shared" si="13"/>
+        <v>1705.8403200000002</v>
+      </c>
+      <c r="J200" s="1">
+        <f t="shared" si="14"/>
+        <v>1569.3730944000004</v>
+      </c>
+      <c r="K200" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L200">
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>180</v>
       </c>
@@ -7163,11 +10383,27 @@
       <c r="G201" s="1">
         <v>1852.79115</v>
       </c>
-      <c r="H201">
+      <c r="H201" s="1">
+        <f t="shared" si="12"/>
+        <v>2093.6539994999998</v>
+      </c>
+      <c r="I201" s="1">
+        <f t="shared" si="13"/>
+        <v>2964.4658400000003</v>
+      </c>
+      <c r="J201" s="1">
+        <f t="shared" si="14"/>
+        <v>2727.3085728000005</v>
+      </c>
+      <c r="K201" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L201">
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>266</v>
       </c>
@@ -7189,11 +10425,27 @@
       <c r="G202" s="1">
         <v>329.92635000000001</v>
       </c>
-      <c r="H202">
+      <c r="H202" s="1">
+        <f t="shared" si="12"/>
+        <v>372.81677550000001</v>
+      </c>
+      <c r="I202" s="1">
+        <f t="shared" si="13"/>
+        <v>527.88216</v>
+      </c>
+      <c r="J202" s="1">
+        <f t="shared" si="14"/>
+        <v>485.65158719999999</v>
+      </c>
+      <c r="K202" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L202">
         <v>21</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>333</v>
       </c>
@@ -7215,11 +10467,27 @@
       <c r="G203" s="1">
         <v>310.94805000000002</v>
       </c>
-      <c r="H203">
+      <c r="H203" s="1">
+        <f t="shared" si="12"/>
+        <v>351.37129649999997</v>
+      </c>
+      <c r="I203" s="1">
+        <f t="shared" si="13"/>
+        <v>497.51688000000007</v>
+      </c>
+      <c r="J203" s="1">
+        <f t="shared" si="14"/>
+        <v>457.71552960000008</v>
+      </c>
+      <c r="K203" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L203">
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>75</v>
       </c>
@@ -7241,11 +10509,27 @@
       <c r="G204" s="1">
         <v>529.26239999999996</v>
       </c>
-      <c r="H204">
+      <c r="H204" s="1">
+        <f t="shared" si="12"/>
+        <v>598.06651199999988</v>
+      </c>
+      <c r="I204" s="1">
+        <f t="shared" si="13"/>
+        <v>846.81984</v>
+      </c>
+      <c r="J204" s="1">
+        <f t="shared" si="14"/>
+        <v>779.07425280000007</v>
+      </c>
+      <c r="K204" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L204">
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>86</v>
       </c>
@@ -7267,11 +10551,27 @@
       <c r="G205" s="1">
         <v>356.63655</v>
       </c>
-      <c r="H205">
+      <c r="H205" s="1">
+        <f t="shared" si="12"/>
+        <v>402.99930149999994</v>
+      </c>
+      <c r="I205" s="1">
+        <f t="shared" si="13"/>
+        <v>570.61847999999998</v>
+      </c>
+      <c r="J205" s="1">
+        <f t="shared" si="14"/>
+        <v>524.96900159999996</v>
+      </c>
+      <c r="K205" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L205">
         <v>20</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>265</v>
       </c>
@@ -7293,11 +10593,27 @@
       <c r="G206" s="1">
         <v>589.65854999999988</v>
       </c>
-      <c r="H206">
+      <c r="H206" s="1">
+        <f t="shared" si="12"/>
+        <v>666.31416149999984</v>
+      </c>
+      <c r="I206" s="1">
+        <f t="shared" si="13"/>
+        <v>943.45367999999985</v>
+      </c>
+      <c r="J206" s="1">
+        <f t="shared" si="14"/>
+        <v>867.97738559999993</v>
+      </c>
+      <c r="K206" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L206">
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>100</v>
       </c>
@@ -7319,11 +10635,27 @@
       <c r="G207" s="1">
         <v>387.53219999999999</v>
       </c>
-      <c r="H207">
+      <c r="H207" s="1">
+        <f t="shared" si="12"/>
+        <v>437.91138599999994</v>
+      </c>
+      <c r="I207" s="1">
+        <f t="shared" si="13"/>
+        <v>620.05151999999998</v>
+      </c>
+      <c r="J207" s="1">
+        <f t="shared" si="14"/>
+        <v>570.4473984</v>
+      </c>
+      <c r="K207" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L207">
         <v>19</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>162</v>
       </c>
@@ -7345,11 +10677,27 @@
       <c r="G208" s="1">
         <v>240.65804999999997</v>
       </c>
-      <c r="H208">
+      <c r="H208" s="1">
+        <f t="shared" si="12"/>
+        <v>271.94359649999996</v>
+      </c>
+      <c r="I208" s="1">
+        <f t="shared" si="13"/>
+        <v>385.05287999999996</v>
+      </c>
+      <c r="J208" s="1">
+        <f t="shared" si="14"/>
+        <v>354.24864959999996</v>
+      </c>
+      <c r="K208" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L208">
         <v>19</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>315</v>
       </c>
@@ -7371,11 +10719,27 @@
       <c r="G209" s="1">
         <v>652.58939999999996</v>
       </c>
-      <c r="H209">
+      <c r="H209" s="1">
+        <f t="shared" si="12"/>
+        <v>737.42602199999988</v>
+      </c>
+      <c r="I209" s="1">
+        <f t="shared" si="13"/>
+        <v>1044.1430399999999</v>
+      </c>
+      <c r="J209" s="1">
+        <f t="shared" si="14"/>
+        <v>960.61159680000003</v>
+      </c>
+      <c r="K209" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L209">
         <v>19</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>189</v>
       </c>
@@ -7397,11 +10761,27 @@
       <c r="G210" s="1">
         <v>7479.5269499999995</v>
       </c>
-      <c r="H210">
+      <c r="H210" s="1">
+        <f t="shared" si="12"/>
+        <v>8451.8654534999987</v>
+      </c>
+      <c r="I210" s="1">
+        <f t="shared" si="13"/>
+        <v>11967.243119999999</v>
+      </c>
+      <c r="J210" s="1">
+        <f t="shared" si="14"/>
+        <v>11009.8636704</v>
+      </c>
+      <c r="K210" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L210">
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>73</v>
       </c>
@@ -7423,11 +10803,27 @@
       <c r="G211" s="1">
         <v>439.73849999999993</v>
       </c>
-      <c r="H211">
+      <c r="H211" s="1">
+        <f t="shared" si="12"/>
+        <v>496.90450499999986</v>
+      </c>
+      <c r="I211" s="1">
+        <f t="shared" si="13"/>
+        <v>703.58159999999998</v>
+      </c>
+      <c r="J211" s="1">
+        <f t="shared" si="14"/>
+        <v>647.295072</v>
+      </c>
+      <c r="K211" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L211">
         <v>17</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>149</v>
       </c>
@@ -7449,11 +10845,27 @@
       <c r="G212" s="1">
         <v>582.74669999999992</v>
       </c>
-      <c r="H212">
+      <c r="H212" s="1">
+        <f t="shared" si="12"/>
+        <v>658.5037709999998</v>
+      </c>
+      <c r="I212" s="1">
+        <f t="shared" si="13"/>
+        <v>932.39471999999989</v>
+      </c>
+      <c r="J212" s="1">
+        <f t="shared" si="14"/>
+        <v>857.80314239999996</v>
+      </c>
+      <c r="K212" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L212">
         <v>17</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>261</v>
       </c>
@@ -7475,11 +10887,27 @@
       <c r="G213" s="1">
         <v>390.9828</v>
       </c>
-      <c r="H213">
+      <c r="H213" s="1">
+        <f t="shared" si="12"/>
+        <v>441.81056399999994</v>
+      </c>
+      <c r="I213" s="1">
+        <f t="shared" si="13"/>
+        <v>625.57248000000004</v>
+      </c>
+      <c r="J213" s="1">
+        <f t="shared" si="14"/>
+        <v>575.52668160000007</v>
+      </c>
+      <c r="K213" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L213">
         <v>17</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>304</v>
       </c>
@@ -7501,11 +10929,27 @@
       <c r="G214" s="1">
         <v>304.18529999999998</v>
       </c>
-      <c r="H214">
+      <c r="H214" s="1">
+        <f t="shared" si="12"/>
+        <v>343.72938899999997</v>
+      </c>
+      <c r="I214" s="1">
+        <f t="shared" si="13"/>
+        <v>486.69648000000001</v>
+      </c>
+      <c r="J214" s="1">
+        <f t="shared" si="14"/>
+        <v>447.76076160000002</v>
+      </c>
+      <c r="K214" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L214">
         <v>17</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>324</v>
       </c>
@@ -7527,11 +10971,27 @@
       <c r="G215" s="1">
         <v>133.58295000000001</v>
       </c>
-      <c r="H215">
+      <c r="H215" s="1">
+        <f t="shared" si="12"/>
+        <v>150.9487335</v>
+      </c>
+      <c r="I215" s="1">
+        <f t="shared" si="13"/>
+        <v>213.73272000000003</v>
+      </c>
+      <c r="J215" s="1">
+        <f t="shared" si="14"/>
+        <v>196.63410240000005</v>
+      </c>
+      <c r="K215" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L215">
         <v>17</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>106</v>
       </c>
@@ -7553,11 +11013,27 @@
       <c r="G216" s="1">
         <v>345.45405</v>
       </c>
-      <c r="H216">
+      <c r="H216" s="1">
+        <f t="shared" si="12"/>
+        <v>390.36307649999998</v>
+      </c>
+      <c r="I216" s="1">
+        <f t="shared" si="13"/>
+        <v>552.72648000000004</v>
+      </c>
+      <c r="J216" s="1">
+        <f t="shared" si="14"/>
+        <v>508.50836160000006</v>
+      </c>
+      <c r="K216" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L216">
         <v>16</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>224</v>
       </c>
@@ -7579,11 +11055,27 @@
       <c r="G217" s="1">
         <v>217.56884999999997</v>
       </c>
-      <c r="H217">
+      <c r="H217" s="1">
+        <f t="shared" si="12"/>
+        <v>245.85280049999994</v>
+      </c>
+      <c r="I217" s="1">
+        <f t="shared" si="13"/>
+        <v>348.11015999999995</v>
+      </c>
+      <c r="J217" s="1">
+        <f t="shared" si="14"/>
+        <v>320.26134719999999</v>
+      </c>
+      <c r="K217" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L217">
         <v>16</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>235</v>
       </c>
@@ -7605,11 +11097,27 @@
       <c r="G218" s="1">
         <v>6420.693299999999</v>
       </c>
-      <c r="H218">
+      <c r="H218" s="1">
+        <f t="shared" si="12"/>
+        <v>7255.3834289999986</v>
+      </c>
+      <c r="I218" s="1">
+        <f t="shared" si="13"/>
+        <v>10273.109279999999</v>
+      </c>
+      <c r="J218" s="1">
+        <f t="shared" si="14"/>
+        <v>9451.2605375999992</v>
+      </c>
+      <c r="K218" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L218">
         <v>16</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>280</v>
       </c>
@@ -7631,11 +11139,27 @@
       <c r="G219" s="1">
         <v>203.24459999999999</v>
       </c>
-      <c r="H219">
+      <c r="H219" s="1">
+        <f t="shared" si="12"/>
+        <v>229.66639799999996</v>
+      </c>
+      <c r="I219" s="1">
+        <f t="shared" si="13"/>
+        <v>325.19136000000003</v>
+      </c>
+      <c r="J219" s="1">
+        <f t="shared" si="14"/>
+        <v>299.17605120000002</v>
+      </c>
+      <c r="K219" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L219">
         <v>16</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>297</v>
       </c>
@@ -7657,11 +11181,27 @@
       <c r="G220" s="1">
         <v>483.78689999999995</v>
       </c>
-      <c r="H220">
+      <c r="H220" s="1">
+        <f t="shared" si="12"/>
+        <v>546.67919699999993</v>
+      </c>
+      <c r="I220" s="1">
+        <f t="shared" si="13"/>
+        <v>774.05903999999998</v>
+      </c>
+      <c r="J220" s="1">
+        <f t="shared" si="14"/>
+        <v>712.13431679999997</v>
+      </c>
+      <c r="K220" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L220">
         <v>16</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>56</v>
       </c>
@@ -7683,11 +11223,27 @@
       <c r="G221" s="1">
         <v>543.58664999999996</v>
       </c>
-      <c r="H221">
+      <c r="H221" s="1">
+        <f t="shared" si="12"/>
+        <v>614.25291449999986</v>
+      </c>
+      <c r="I221" s="1">
+        <f t="shared" si="13"/>
+        <v>869.73864000000003</v>
+      </c>
+      <c r="J221" s="1">
+        <f t="shared" si="14"/>
+        <v>800.15954880000004</v>
+      </c>
+      <c r="K221" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L221">
         <v>15</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -7709,11 +11265,27 @@
       <c r="G222" s="1">
         <v>135.60645</v>
       </c>
-      <c r="H222">
+      <c r="H222" s="1">
+        <f t="shared" si="12"/>
+        <v>153.23528849999997</v>
+      </c>
+      <c r="I222" s="1">
+        <f t="shared" si="13"/>
+        <v>216.97032000000002</v>
+      </c>
+      <c r="J222" s="1">
+        <f t="shared" si="14"/>
+        <v>199.61269440000001</v>
+      </c>
+      <c r="K222" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L222">
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>140</v>
       </c>
@@ -7735,11 +11307,27 @@
       <c r="G223" s="1">
         <v>194.7885</v>
       </c>
-      <c r="H223">
+      <c r="H223" s="1">
+        <f t="shared" si="12"/>
+        <v>220.11100499999998</v>
+      </c>
+      <c r="I223" s="1">
+        <f t="shared" si="13"/>
+        <v>311.66160000000002</v>
+      </c>
+      <c r="J223" s="1">
+        <f t="shared" si="14"/>
+        <v>286.72867200000002</v>
+      </c>
+      <c r="K223" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L223">
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>276</v>
       </c>
@@ -7761,11 +11349,27 @@
       <c r="G224" s="1">
         <v>785.26710000000003</v>
       </c>
-      <c r="H224">
+      <c r="H224" s="1">
+        <f t="shared" si="12"/>
+        <v>887.35182299999997</v>
+      </c>
+      <c r="I224" s="1">
+        <f t="shared" si="13"/>
+        <v>1256.4273600000001</v>
+      </c>
+      <c r="J224" s="1">
+        <f t="shared" si="14"/>
+        <v>1155.9131712000001</v>
+      </c>
+      <c r="K224" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L224">
         <v>15</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>294</v>
       </c>
@@ -7787,11 +11391,27 @@
       <c r="G225" s="1">
         <v>483.78689999999995</v>
       </c>
-      <c r="H225">
+      <c r="H225" s="1">
+        <f t="shared" si="12"/>
+        <v>546.67919699999993</v>
+      </c>
+      <c r="I225" s="1">
+        <f t="shared" si="13"/>
+        <v>774.05903999999998</v>
+      </c>
+      <c r="J225" s="1">
+        <f t="shared" si="14"/>
+        <v>712.13431679999997</v>
+      </c>
+      <c r="K225" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L225">
         <v>15</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>337</v>
       </c>
@@ -7813,11 +11433,27 @@
       <c r="G226" s="1">
         <v>253.91729999999998</v>
       </c>
-      <c r="H226">
+      <c r="H226" s="1">
+        <f t="shared" si="12"/>
+        <v>286.92654899999997</v>
+      </c>
+      <c r="I226" s="1">
+        <f t="shared" si="13"/>
+        <v>406.26767999999998</v>
+      </c>
+      <c r="J226" s="1">
+        <f t="shared" si="14"/>
+        <v>373.7662656</v>
+      </c>
+      <c r="K226" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L226">
         <v>15</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>238</v>
       </c>
@@ -7839,11 +11475,27 @@
       <c r="G227" s="1">
         <v>1233.47235</v>
       </c>
-      <c r="H227">
+      <c r="H227" s="1">
+        <f t="shared" si="12"/>
+        <v>1393.8237554999998</v>
+      </c>
+      <c r="I227" s="1">
+        <f t="shared" si="13"/>
+        <v>1973.5557600000002</v>
+      </c>
+      <c r="J227" s="1">
+        <f t="shared" si="14"/>
+        <v>1815.6712992000002</v>
+      </c>
+      <c r="K227" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L227">
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>254</v>
       </c>
@@ -7865,11 +11517,27 @@
       <c r="G228" s="1">
         <v>304.90949999999998</v>
       </c>
-      <c r="H228">
+      <c r="H228" s="1">
+        <f t="shared" si="12"/>
+        <v>344.54773499999993</v>
+      </c>
+      <c r="I228" s="1">
+        <f t="shared" si="13"/>
+        <v>487.85519999999997</v>
+      </c>
+      <c r="J228" s="1">
+        <f t="shared" si="14"/>
+        <v>448.82678399999998</v>
+      </c>
+      <c r="K228" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L228">
         <v>14</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>220</v>
       </c>
@@ -7891,11 +11559,27 @@
       <c r="G229" s="1">
         <v>1168.4008499999998</v>
       </c>
-      <c r="H229">
+      <c r="H229" s="1">
+        <f t="shared" si="12"/>
+        <v>1320.2929604999997</v>
+      </c>
+      <c r="I229" s="1">
+        <f t="shared" si="13"/>
+        <v>1869.4413599999998</v>
+      </c>
+      <c r="J229" s="1">
+        <f t="shared" si="14"/>
+        <v>1719.8860511999999</v>
+      </c>
+      <c r="K229" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L229">
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>331</v>
       </c>
@@ -7917,11 +11601,27 @@
       <c r="G230" s="1">
         <v>672.62205000000006</v>
       </c>
-      <c r="H230">
+      <c r="H230" s="1">
+        <f t="shared" si="12"/>
+        <v>760.06291650000003</v>
+      </c>
+      <c r="I230" s="1">
+        <f t="shared" si="13"/>
+        <v>1076.1952800000001</v>
+      </c>
+      <c r="J230" s="1">
+        <f t="shared" si="14"/>
+        <v>990.09965760000011</v>
+      </c>
+      <c r="K230" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L230">
         <v>13</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>124</v>
       </c>
@@ -7943,11 +11643,27 @@
       <c r="G231" s="1">
         <v>345.00674999999995</v>
       </c>
-      <c r="H231">
+      <c r="H231" s="1">
+        <f t="shared" si="12"/>
+        <v>389.85762749999992</v>
+      </c>
+      <c r="I231" s="1">
+        <f t="shared" si="13"/>
+        <v>552.0107999999999</v>
+      </c>
+      <c r="J231" s="1">
+        <f t="shared" si="14"/>
+        <v>507.84993599999996</v>
+      </c>
+      <c r="K231" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L231">
         <v>12</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>296</v>
       </c>
@@ -7969,11 +11685,27 @@
       <c r="G232" s="1">
         <v>245.08844999999999</v>
       </c>
-      <c r="H232">
+      <c r="H232" s="1">
+        <f t="shared" si="12"/>
+        <v>276.94994849999995</v>
+      </c>
+      <c r="I232" s="1">
+        <f t="shared" si="13"/>
+        <v>392.14152000000001</v>
+      </c>
+      <c r="J232" s="1">
+        <f t="shared" si="14"/>
+        <v>360.77019840000003</v>
+      </c>
+      <c r="K232" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L232">
         <v>12</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>8</v>
       </c>
@@ -7995,11 +11727,27 @@
       <c r="G233" s="1">
         <v>618.79694999999992</v>
       </c>
-      <c r="H233">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H233" s="1">
+        <f t="shared" si="12"/>
+        <v>699.24055349999981</v>
+      </c>
+      <c r="I233" s="1">
+        <f t="shared" si="13"/>
+        <v>990.07511999999997</v>
+      </c>
+      <c r="J233" s="1">
+        <f t="shared" si="14"/>
+        <v>910.86911040000007</v>
+      </c>
+      <c r="K233" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L233">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>21</v>
       </c>
@@ -8021,11 +11769,27 @@
       <c r="G234" s="1">
         <v>271.67084999999997</v>
       </c>
-      <c r="H234">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H234" s="1">
+        <f t="shared" si="12"/>
+        <v>306.98806049999996</v>
+      </c>
+      <c r="I234" s="1">
+        <f t="shared" si="13"/>
+        <v>434.67336</v>
+      </c>
+      <c r="J234" s="1">
+        <f t="shared" si="14"/>
+        <v>399.8994912</v>
+      </c>
+      <c r="K234" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L234">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>191</v>
       </c>
@@ -8047,11 +11811,27 @@
       <c r="G235" s="1">
         <v>5292.2725500000006</v>
       </c>
-      <c r="H235">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H235" s="1">
+        <f t="shared" si="12"/>
+        <v>5980.2679815000001</v>
+      </c>
+      <c r="I235" s="1">
+        <f t="shared" si="13"/>
+        <v>8467.636080000002</v>
+      </c>
+      <c r="J235" s="1">
+        <f t="shared" si="14"/>
+        <v>7790.2251936000021</v>
+      </c>
+      <c r="K235" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L235">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>205</v>
       </c>
@@ -8073,11 +11853,27 @@
       <c r="G236" s="1">
         <v>760.72949999999992</v>
       </c>
-      <c r="H236">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H236" s="1">
+        <f t="shared" si="12"/>
+        <v>859.62433499999986</v>
+      </c>
+      <c r="I236" s="1">
+        <f t="shared" si="13"/>
+        <v>1217.1671999999999</v>
+      </c>
+      <c r="J236" s="1">
+        <f t="shared" si="14"/>
+        <v>1119.7938239999999</v>
+      </c>
+      <c r="K236" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L236">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>322</v>
       </c>
@@ -8099,11 +11895,27 @@
       <c r="G237" s="1">
         <v>158.50395</v>
       </c>
-      <c r="H237">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H237" s="1">
+        <f t="shared" si="12"/>
+        <v>179.10946349999998</v>
+      </c>
+      <c r="I237" s="1">
+        <f t="shared" si="13"/>
+        <v>253.60632000000001</v>
+      </c>
+      <c r="J237" s="1">
+        <f t="shared" si="14"/>
+        <v>233.31781440000003</v>
+      </c>
+      <c r="K237" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L237">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>153</v>
       </c>
@@ -8125,11 +11937,27 @@
       <c r="G238" s="1">
         <v>2067.8785499999999</v>
       </c>
-      <c r="H238">
+      <c r="H238" s="1">
+        <f t="shared" si="12"/>
+        <v>2336.7027614999997</v>
+      </c>
+      <c r="I238" s="1">
+        <f t="shared" si="13"/>
+        <v>3308.6056800000001</v>
+      </c>
+      <c r="J238" s="1">
+        <f t="shared" si="14"/>
+        <v>3043.9172256000002</v>
+      </c>
+      <c r="K238" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L238">
         <v>10</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>207</v>
       </c>
@@ -8151,11 +11979,27 @@
       <c r="G239" s="1">
         <v>760.72949999999992</v>
       </c>
-      <c r="H239">
+      <c r="H239" s="1">
+        <f t="shared" si="12"/>
+        <v>859.62433499999986</v>
+      </c>
+      <c r="I239" s="1">
+        <f t="shared" si="13"/>
+        <v>1217.1671999999999</v>
+      </c>
+      <c r="J239" s="1">
+        <f t="shared" si="14"/>
+        <v>1119.7938239999999</v>
+      </c>
+      <c r="K239" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L239">
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>239</v>
       </c>
@@ -8177,11 +12021,27 @@
       <c r="G240" s="1">
         <v>2553.5185499999998</v>
       </c>
-      <c r="H240">
+      <c r="H240" s="1">
+        <f t="shared" si="12"/>
+        <v>2885.4759614999994</v>
+      </c>
+      <c r="I240" s="1">
+        <f t="shared" si="13"/>
+        <v>4085.62968</v>
+      </c>
+      <c r="J240" s="1">
+        <f t="shared" si="14"/>
+        <v>3758.7793056</v>
+      </c>
+      <c r="K240" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L240">
         <v>10</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>290</v>
       </c>
@@ -8203,11 +12063,27 @@
       <c r="G241" s="1">
         <v>245.08844999999999</v>
       </c>
-      <c r="H241">
+      <c r="H241" s="1">
+        <f t="shared" si="12"/>
+        <v>276.94994849999995</v>
+      </c>
+      <c r="I241" s="1">
+        <f t="shared" si="13"/>
+        <v>392.14152000000001</v>
+      </c>
+      <c r="J241" s="1">
+        <f t="shared" si="14"/>
+        <v>360.77019840000003</v>
+      </c>
+      <c r="K241" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L241">
         <v>10</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>334</v>
       </c>
@@ -8229,11 +12105,27 @@
       <c r="G242" s="1">
         <v>850.57289999999989</v>
       </c>
-      <c r="H242">
+      <c r="H242" s="1">
+        <f t="shared" si="12"/>
+        <v>961.14737699999978</v>
+      </c>
+      <c r="I242" s="1">
+        <f t="shared" si="13"/>
+        <v>1360.9166399999999</v>
+      </c>
+      <c r="J242" s="1">
+        <f t="shared" si="14"/>
+        <v>1252.0433088</v>
+      </c>
+      <c r="K242" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L242">
         <v>10</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>363</v>
       </c>
@@ -8255,11 +12147,27 @@
       <c r="G243" s="1">
         <v>710.49344999999994</v>
       </c>
-      <c r="H243">
+      <c r="H243" s="1">
+        <f t="shared" si="12"/>
+        <v>802.85759849999988</v>
+      </c>
+      <c r="I243" s="1">
+        <f t="shared" si="13"/>
+        <v>1136.78952</v>
+      </c>
+      <c r="J243" s="1">
+        <f t="shared" si="14"/>
+        <v>1045.8463584000001</v>
+      </c>
+      <c r="K243" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L243">
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>76</v>
       </c>
@@ -8281,11 +12189,27 @@
       <c r="G244" s="1">
         <v>314.38799999999998</v>
       </c>
-      <c r="H244">
+      <c r="H244" s="1">
+        <f t="shared" si="12"/>
+        <v>355.25843999999995</v>
+      </c>
+      <c r="I244" s="1">
+        <f t="shared" si="13"/>
+        <v>503.02080000000001</v>
+      </c>
+      <c r="J244" s="1">
+        <f t="shared" si="14"/>
+        <v>462.77913600000005</v>
+      </c>
+      <c r="K244" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L244">
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>215</v>
       </c>
@@ -8307,11 +12231,27 @@
       <c r="G245" s="1">
         <v>703.59224999999992</v>
       </c>
-      <c r="H245">
+      <c r="H245" s="1">
+        <f t="shared" si="12"/>
+        <v>795.05924249999987</v>
+      </c>
+      <c r="I245" s="1">
+        <f t="shared" si="13"/>
+        <v>1125.7475999999999</v>
+      </c>
+      <c r="J245" s="1">
+        <f t="shared" si="14"/>
+        <v>1035.6877919999999</v>
+      </c>
+      <c r="K245" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L245">
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>255</v>
       </c>
@@ -8333,11 +12273,27 @@
       <c r="G246" s="1">
         <v>537.69719999999995</v>
       </c>
-      <c r="H246">
+      <c r="H246" s="1">
+        <f t="shared" si="12"/>
+        <v>607.59783599999992</v>
+      </c>
+      <c r="I246" s="1">
+        <f t="shared" si="13"/>
+        <v>860.31551999999999</v>
+      </c>
+      <c r="J246" s="1">
+        <f t="shared" si="14"/>
+        <v>791.49027840000008</v>
+      </c>
+      <c r="K246" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L246">
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>111</v>
       </c>
@@ -8359,11 +12315,27 @@
       <c r="G247" s="1">
         <v>545.05634999999995</v>
       </c>
-      <c r="H247">
+      <c r="H247" s="1">
+        <f t="shared" si="12"/>
+        <v>615.91367549999984</v>
+      </c>
+      <c r="I247" s="1">
+        <f t="shared" si="13"/>
+        <v>872.09015999999997</v>
+      </c>
+      <c r="J247" s="1">
+        <f t="shared" si="14"/>
+        <v>802.32294720000004</v>
+      </c>
+      <c r="K247" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L247">
         <v>8</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>329</v>
       </c>
@@ -8385,11 +12357,27 @@
       <c r="G248" s="1">
         <v>168.18479999999997</v>
       </c>
-      <c r="H248">
+      <c r="H248" s="1">
+        <f t="shared" si="12"/>
+        <v>190.04882399999994</v>
+      </c>
+      <c r="I248" s="1">
+        <f t="shared" si="13"/>
+        <v>269.09567999999996</v>
+      </c>
+      <c r="J248" s="1">
+        <f t="shared" si="14"/>
+        <v>247.56802559999997</v>
+      </c>
+      <c r="K248" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L248">
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>68</v>
       </c>
@@ -8411,11 +12399,27 @@
       <c r="G249" s="1">
         <v>246.87764999999999</v>
       </c>
-      <c r="H249">
+      <c r="H249" s="1">
+        <f t="shared" si="12"/>
+        <v>278.97174449999994</v>
+      </c>
+      <c r="I249" s="1">
+        <f t="shared" si="13"/>
+        <v>395.00423999999998</v>
+      </c>
+      <c r="J249" s="1">
+        <f t="shared" si="14"/>
+        <v>363.40390079999997</v>
+      </c>
+      <c r="K249" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L249">
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>385</v>
       </c>
@@ -8437,11 +12441,27 @@
       <c r="G250" s="1">
         <v>172.83884999999998</v>
       </c>
-      <c r="H250">
+      <c r="H250" s="1">
+        <f t="shared" si="12"/>
+        <v>195.30790049999996</v>
+      </c>
+      <c r="I250" s="1">
+        <f t="shared" si="13"/>
+        <v>276.54215999999997</v>
+      </c>
+      <c r="J250" s="1">
+        <f t="shared" si="14"/>
+        <v>254.41878719999997</v>
+      </c>
+      <c r="K250" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L250">
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>44</v>
       </c>
@@ -8463,11 +12483,27 @@
       <c r="G251" s="1">
         <v>811.65779999999995</v>
       </c>
-      <c r="H251">
+      <c r="H251" s="1">
+        <f t="shared" si="12"/>
+        <v>917.17331399999989</v>
+      </c>
+      <c r="I251" s="1">
+        <f t="shared" si="13"/>
+        <v>1298.65248</v>
+      </c>
+      <c r="J251" s="1">
+        <f t="shared" si="14"/>
+        <v>1194.7602816000001</v>
+      </c>
+      <c r="K251" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L251">
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>52</v>
       </c>
@@ -8489,11 +12525,27 @@
       <c r="G252" s="1">
         <v>812.19029999999998</v>
       </c>
-      <c r="H252">
+      <c r="H252" s="1">
+        <f t="shared" si="12"/>
+        <v>917.77503899999988</v>
+      </c>
+      <c r="I252" s="1">
+        <f t="shared" si="13"/>
+        <v>1299.5044800000001</v>
+      </c>
+      <c r="J252" s="1">
+        <f t="shared" si="14"/>
+        <v>1195.5441216000002</v>
+      </c>
+      <c r="K252" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L252">
         <v>6</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>112</v>
       </c>
@@ -8515,11 +12567,27 @@
       <c r="G253" s="1">
         <v>3633.5989499999996</v>
       </c>
-      <c r="H253">
+      <c r="H253" s="1">
+        <f t="shared" si="12"/>
+        <v>4105.9668134999993</v>
+      </c>
+      <c r="I253" s="1">
+        <f t="shared" si="13"/>
+        <v>5813.7583199999999</v>
+      </c>
+      <c r="J253" s="1">
+        <f t="shared" si="14"/>
+        <v>5348.6576544</v>
+      </c>
+      <c r="K253" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L253">
         <v>6</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>219</v>
       </c>
@@ -8541,11 +12609,27 @@
       <c r="G254" s="1">
         <v>750.07949999999994</v>
       </c>
-      <c r="H254">
+      <c r="H254" s="1">
+        <f t="shared" si="12"/>
+        <v>847.58983499999988</v>
+      </c>
+      <c r="I254" s="1">
+        <f t="shared" si="13"/>
+        <v>1200.1271999999999</v>
+      </c>
+      <c r="J254" s="1">
+        <f t="shared" si="14"/>
+        <v>1104.1170239999999</v>
+      </c>
+      <c r="K254" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L254">
         <v>6</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>221</v>
       </c>
@@ -8567,11 +12651,27 @@
       <c r="G255" s="1">
         <v>637.65809999999999</v>
       </c>
-      <c r="H255">
+      <c r="H255" s="1">
+        <f t="shared" si="12"/>
+        <v>720.55365299999994</v>
+      </c>
+      <c r="I255" s="1">
+        <f t="shared" si="13"/>
+        <v>1020.25296</v>
+      </c>
+      <c r="J255" s="1">
+        <f t="shared" si="14"/>
+        <v>938.6327232000001</v>
+      </c>
+      <c r="K255" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L255">
         <v>6</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>295</v>
       </c>
@@ -8593,11 +12693,27 @@
       <c r="G256" s="1">
         <v>277.63484999999997</v>
       </c>
-      <c r="H256">
+      <c r="H256" s="1">
+        <f t="shared" si="12"/>
+        <v>313.72738049999992</v>
+      </c>
+      <c r="I256" s="1">
+        <f t="shared" si="13"/>
+        <v>444.21575999999999</v>
+      </c>
+      <c r="J256" s="1">
+        <f t="shared" si="14"/>
+        <v>408.67849920000003</v>
+      </c>
+      <c r="K256" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L256">
         <v>6</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>402</v>
       </c>
@@ -8619,11 +12735,27 @@
       <c r="G257" s="1">
         <v>139.13159999999999</v>
       </c>
-      <c r="H257">
+      <c r="H257" s="1">
+        <f t="shared" si="12"/>
+        <v>157.21870799999996</v>
+      </c>
+      <c r="I257" s="1">
+        <f t="shared" si="13"/>
+        <v>222.61055999999999</v>
+      </c>
+      <c r="J257" s="1">
+        <f t="shared" si="14"/>
+        <v>204.80171519999999</v>
+      </c>
+      <c r="K257" s="6">
+        <f t="shared" si="15"/>
+        <v>1.472</v>
+      </c>
+      <c r="L257">
         <v>6</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>88</v>
       </c>
@@ -8645,11 +12777,27 @@
       <c r="G258" s="1">
         <v>151.11284999999998</v>
       </c>
-      <c r="H258">
+      <c r="H258" s="1">
+        <f t="shared" si="12"/>
+        <v>170.75752049999997</v>
+      </c>
+      <c r="I258" s="1">
+        <f t="shared" si="13"/>
+        <v>241.78055999999998</v>
+      </c>
+      <c r="J258" s="1">
+        <f t="shared" si="14"/>
+        <v>222.4381152</v>
+      </c>
+      <c r="K258" s="6">
+        <f t="shared" si="15"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L258">
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>150</v>
       </c>
@@ -8671,11 +12819,27 @@
       <c r="G259" s="1">
         <v>1214.8880999999999</v>
       </c>
-      <c r="H259">
+      <c r="H259" s="1">
+        <f t="shared" ref="H259:H295" si="16">G259*1.13</f>
+        <v>1372.8235529999997</v>
+      </c>
+      <c r="I259" s="1">
+        <f t="shared" ref="I259:I295" si="17">G259*1.6</f>
+        <v>1943.82096</v>
+      </c>
+      <c r="J259" s="1">
+        <f t="shared" ref="J259:J295" si="18">I259*0.92</f>
+        <v>1788.3152832000001</v>
+      </c>
+      <c r="K259" s="6">
+        <f t="shared" ref="K259:K295" si="19">J259/G259</f>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L259">
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>212</v>
       </c>
@@ -8697,11 +12861,27 @@
       <c r="G260" s="1">
         <v>710.68514999999991</v>
       </c>
-      <c r="H260">
+      <c r="H260" s="1">
+        <f t="shared" si="16"/>
+        <v>803.0742194999998</v>
+      </c>
+      <c r="I260" s="1">
+        <f t="shared" si="17"/>
+        <v>1137.0962399999999</v>
+      </c>
+      <c r="J260" s="1">
+        <f t="shared" si="18"/>
+        <v>1046.1285407999999</v>
+      </c>
+      <c r="K260" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L260">
         <v>5</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>360</v>
       </c>
@@ -8723,11 +12903,27 @@
       <c r="G261" s="1">
         <v>991.93034999999998</v>
       </c>
-      <c r="H261">
+      <c r="H261" s="1">
+        <f t="shared" si="16"/>
+        <v>1120.8812954999999</v>
+      </c>
+      <c r="I261" s="1">
+        <f t="shared" si="17"/>
+        <v>1587.0885600000001</v>
+      </c>
+      <c r="J261" s="1">
+        <f t="shared" si="18"/>
+        <v>1460.1214752000003</v>
+      </c>
+      <c r="K261" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000004</v>
+      </c>
+      <c r="L261">
         <v>5</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>48</v>
       </c>
@@ -8749,11 +12945,27 @@
       <c r="G262" s="1">
         <v>812.19029999999998</v>
       </c>
-      <c r="H262">
+      <c r="H262" s="1">
+        <f t="shared" si="16"/>
+        <v>917.77503899999988</v>
+      </c>
+      <c r="I262" s="1">
+        <f t="shared" si="17"/>
+        <v>1299.5044800000001</v>
+      </c>
+      <c r="J262" s="1">
+        <f t="shared" si="18"/>
+        <v>1195.5441216000002</v>
+      </c>
+      <c r="K262" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L262">
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>112</v>
       </c>
@@ -8775,11 +12987,27 @@
       <c r="G263" s="1">
         <v>2172.1100999999999</v>
       </c>
-      <c r="H263">
+      <c r="H263" s="1">
+        <f t="shared" si="16"/>
+        <v>2454.4844129999997</v>
+      </c>
+      <c r="I263" s="1">
+        <f t="shared" si="17"/>
+        <v>3475.3761599999998</v>
+      </c>
+      <c r="J263" s="1">
+        <f t="shared" si="18"/>
+        <v>3197.3460672000001</v>
+      </c>
+      <c r="K263" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L263">
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>151</v>
       </c>
@@ -8801,11 +13029,27 @@
       <c r="G264" s="1">
         <v>2497.7445000000002</v>
       </c>
-      <c r="H264">
+      <c r="H264" s="1">
+        <f t="shared" si="16"/>
+        <v>2822.4512850000001</v>
+      </c>
+      <c r="I264" s="1">
+        <f t="shared" si="17"/>
+        <v>3996.3912000000005</v>
+      </c>
+      <c r="J264" s="1">
+        <f t="shared" si="18"/>
+        <v>3676.6799040000005</v>
+      </c>
+      <c r="K264" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L264">
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>244</v>
       </c>
@@ -8827,11 +13071,27 @@
       <c r="G265" s="1">
         <v>2181.6844500000002</v>
       </c>
-      <c r="H265">
+      <c r="H265" s="1">
+        <f t="shared" si="16"/>
+        <v>2465.3034284999999</v>
+      </c>
+      <c r="I265" s="1">
+        <f t="shared" si="17"/>
+        <v>3490.6951200000003</v>
+      </c>
+      <c r="J265" s="1">
+        <f t="shared" si="18"/>
+        <v>3211.4395104000005</v>
+      </c>
+      <c r="K265" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L265">
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>267</v>
       </c>
@@ -8853,11 +13113,27 @@
       <c r="G266" s="1">
         <v>2386.7395500000002</v>
       </c>
-      <c r="H266">
+      <c r="H266" s="1">
+        <f t="shared" si="16"/>
+        <v>2697.0156915000002</v>
+      </c>
+      <c r="I266" s="1">
+        <f t="shared" si="17"/>
+        <v>3818.7832800000006</v>
+      </c>
+      <c r="J266" s="1">
+        <f t="shared" si="18"/>
+        <v>3513.2806176000008</v>
+      </c>
+      <c r="K266" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L266">
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>300</v>
       </c>
@@ -8879,11 +13155,27 @@
       <c r="G267" s="1">
         <v>378.62879999999996</v>
       </c>
-      <c r="H267">
+      <c r="H267" s="1">
+        <f t="shared" si="16"/>
+        <v>427.8505439999999</v>
+      </c>
+      <c r="I267" s="1">
+        <f t="shared" si="17"/>
+        <v>605.80607999999995</v>
+      </c>
+      <c r="J267" s="1">
+        <f t="shared" si="18"/>
+        <v>557.34159360000001</v>
+      </c>
+      <c r="K267" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L267">
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>310</v>
       </c>
@@ -8905,11 +13197,27 @@
       <c r="G268" s="1">
         <v>347.5095</v>
       </c>
-      <c r="H268">
+      <c r="H268" s="1">
+        <f t="shared" si="16"/>
+        <v>392.68573499999997</v>
+      </c>
+      <c r="I268" s="1">
+        <f t="shared" si="17"/>
+        <v>556.01520000000005</v>
+      </c>
+      <c r="J268" s="1">
+        <f t="shared" si="18"/>
+        <v>511.53398400000009</v>
+      </c>
+      <c r="K268" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L268">
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>352</v>
       </c>
@@ -8931,11 +13239,27 @@
       <c r="G269" s="1">
         <v>1226.9332499999998</v>
       </c>
-      <c r="H269">
+      <c r="H269" s="1">
+        <f t="shared" si="16"/>
+        <v>1386.4345724999996</v>
+      </c>
+      <c r="I269" s="1">
+        <f t="shared" si="17"/>
+        <v>1963.0931999999998</v>
+      </c>
+      <c r="J269" s="1">
+        <f t="shared" si="18"/>
+        <v>1806.0457439999998</v>
+      </c>
+      <c r="K269" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L269">
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>354</v>
       </c>
@@ -8957,11 +13281,27 @@
       <c r="G270" s="1">
         <v>1226.9332499999998</v>
       </c>
-      <c r="H270">
+      <c r="H270" s="1">
+        <f t="shared" si="16"/>
+        <v>1386.4345724999996</v>
+      </c>
+      <c r="I270" s="1">
+        <f t="shared" si="17"/>
+        <v>1963.0931999999998</v>
+      </c>
+      <c r="J270" s="1">
+        <f t="shared" si="18"/>
+        <v>1806.0457439999998</v>
+      </c>
+      <c r="K270" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L270">
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>357</v>
       </c>
@@ -8983,11 +13323,27 @@
       <c r="G271" s="1">
         <v>1226.9332499999998</v>
       </c>
-      <c r="H271">
+      <c r="H271" s="1">
+        <f t="shared" si="16"/>
+        <v>1386.4345724999996</v>
+      </c>
+      <c r="I271" s="1">
+        <f t="shared" si="17"/>
+        <v>1963.0931999999998</v>
+      </c>
+      <c r="J271" s="1">
+        <f t="shared" si="18"/>
+        <v>1806.0457439999998</v>
+      </c>
+      <c r="K271" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L271">
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>359</v>
       </c>
@@ -9009,11 +13365,27 @@
       <c r="G272" s="1">
         <v>1579.4269499999998</v>
       </c>
-      <c r="H272">
+      <c r="H272" s="1">
+        <f t="shared" si="16"/>
+        <v>1784.7524534999995</v>
+      </c>
+      <c r="I272" s="1">
+        <f t="shared" si="17"/>
+        <v>2527.0831199999998</v>
+      </c>
+      <c r="J272" s="1">
+        <f t="shared" si="18"/>
+        <v>2324.9164704</v>
+      </c>
+      <c r="K272" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L272">
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>371</v>
       </c>
@@ -9035,11 +13407,27 @@
       <c r="G273" s="1">
         <v>329.87309999999997</v>
       </c>
-      <c r="H273">
+      <c r="H273" s="1">
+        <f t="shared" si="16"/>
+        <v>372.75660299999993</v>
+      </c>
+      <c r="I273" s="1">
+        <f t="shared" si="17"/>
+        <v>527.79696000000001</v>
+      </c>
+      <c r="J273" s="1">
+        <f t="shared" si="18"/>
+        <v>485.57320320000002</v>
+      </c>
+      <c r="K273" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L273">
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>48</v>
       </c>
@@ -9061,11 +13449,27 @@
       <c r="G274" s="1">
         <v>933.9197999999999</v>
       </c>
-      <c r="H274">
+      <c r="H274" s="1">
+        <f t="shared" si="16"/>
+        <v>1055.3293739999997</v>
+      </c>
+      <c r="I274" s="1">
+        <f t="shared" si="17"/>
+        <v>1494.2716799999998</v>
+      </c>
+      <c r="J274" s="1">
+        <f t="shared" si="18"/>
+        <v>1374.7299455999998</v>
+      </c>
+      <c r="K274" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L274">
         <v>3</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>209</v>
       </c>
@@ -9087,11 +13491,27 @@
       <c r="G275" s="1">
         <v>463.23239999999993</v>
       </c>
-      <c r="H275">
+      <c r="H275" s="1">
+        <f t="shared" si="16"/>
+        <v>523.45261199999982</v>
+      </c>
+      <c r="I275" s="1">
+        <f t="shared" si="17"/>
+        <v>741.17183999999997</v>
+      </c>
+      <c r="J275" s="1">
+        <f t="shared" si="18"/>
+        <v>681.87809279999999</v>
+      </c>
+      <c r="K275" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L275">
         <v>3</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>365</v>
       </c>
@@ -9113,11 +13533,27 @@
       <c r="G276" s="1">
         <v>439.68525</v>
       </c>
-      <c r="H276">
+      <c r="H276" s="1">
+        <f t="shared" si="16"/>
+        <v>496.84433249999995</v>
+      </c>
+      <c r="I276" s="1">
+        <f t="shared" si="17"/>
+        <v>703.49639999999999</v>
+      </c>
+      <c r="J276" s="1">
+        <f t="shared" si="18"/>
+        <v>647.21668799999998</v>
+      </c>
+      <c r="K276" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L276">
         <v>3</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>42</v>
       </c>
@@ -9139,11 +13575,27 @@
       <c r="G277" s="1">
         <v>2189.3524499999999</v>
       </c>
-      <c r="H277">
+      <c r="H277" s="1">
+        <f t="shared" si="16"/>
+        <v>2473.9682684999998</v>
+      </c>
+      <c r="I277" s="1">
+        <f t="shared" si="17"/>
+        <v>3502.9639200000001</v>
+      </c>
+      <c r="J277" s="1">
+        <f t="shared" si="18"/>
+        <v>3222.7268064000004</v>
+      </c>
+      <c r="K277" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L277">
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>114</v>
       </c>
@@ -9165,11 +13617,27 @@
       <c r="G278" s="1">
         <v>690.13064999999995</v>
       </c>
-      <c r="H278">
+      <c r="H278" s="1">
+        <f t="shared" si="16"/>
+        <v>779.84763449999991</v>
+      </c>
+      <c r="I278" s="1">
+        <f t="shared" si="17"/>
+        <v>1104.20904</v>
+      </c>
+      <c r="J278" s="1">
+        <f t="shared" si="18"/>
+        <v>1015.8723168</v>
+      </c>
+      <c r="K278" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L278">
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>154</v>
       </c>
@@ -9191,11 +13659,27 @@
       <c r="G279" s="1">
         <v>17701.311750000001</v>
       </c>
-      <c r="H279">
+      <c r="H279" s="1">
+        <f t="shared" si="16"/>
+        <v>20002.482277499999</v>
+      </c>
+      <c r="I279" s="1">
+        <f t="shared" si="17"/>
+        <v>28322.098800000003</v>
+      </c>
+      <c r="J279" s="1">
+        <f t="shared" si="18"/>
+        <v>26056.330896000003</v>
+      </c>
+      <c r="K279" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L279">
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>257</v>
       </c>
@@ -9217,11 +13701,27 @@
       <c r="G280" s="1">
         <v>1701.8380499999998</v>
       </c>
-      <c r="H280">
+      <c r="H280" s="1">
+        <f t="shared" si="16"/>
+        <v>1923.0769964999997</v>
+      </c>
+      <c r="I280" s="1">
+        <f t="shared" si="17"/>
+        <v>2722.9408800000001</v>
+      </c>
+      <c r="J280" s="1">
+        <f t="shared" si="18"/>
+        <v>2505.1056096000002</v>
+      </c>
+      <c r="K280" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L280">
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>317</v>
       </c>
@@ -9243,11 +13743,27 @@
       <c r="G281" s="1">
         <v>124.74345</v>
       </c>
-      <c r="H281">
+      <c r="H281" s="1">
+        <f t="shared" si="16"/>
+        <v>140.96009849999999</v>
+      </c>
+      <c r="I281" s="1">
+        <f t="shared" si="17"/>
+        <v>199.58951999999999</v>
+      </c>
+      <c r="J281" s="1">
+        <f t="shared" si="18"/>
+        <v>183.6223584</v>
+      </c>
+      <c r="K281" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L281">
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>366</v>
       </c>
@@ -9269,11 +13785,27 @@
       <c r="G282" s="1">
         <v>726.5643</v>
       </c>
-      <c r="H282">
+      <c r="H282" s="1">
+        <f t="shared" si="16"/>
+        <v>821.01765899999998</v>
+      </c>
+      <c r="I282" s="1">
+        <f t="shared" si="17"/>
+        <v>1162.50288</v>
+      </c>
+      <c r="J282" s="1">
+        <f t="shared" si="18"/>
+        <v>1069.5026496</v>
+      </c>
+      <c r="K282" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L282">
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>369</v>
       </c>
@@ -9295,11 +13827,27 @@
       <c r="G283" s="1">
         <v>150.8253</v>
       </c>
-      <c r="H283">
+      <c r="H283" s="1">
+        <f t="shared" si="16"/>
+        <v>170.43258899999998</v>
+      </c>
+      <c r="I283" s="1">
+        <f t="shared" si="17"/>
+        <v>241.32048</v>
+      </c>
+      <c r="J283" s="1">
+        <f t="shared" si="18"/>
+        <v>222.01484160000001</v>
+      </c>
+      <c r="K283" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L283">
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>373</v>
       </c>
@@ -9321,11 +13869,27 @@
       <c r="G284" s="1">
         <v>989.64059999999995</v>
       </c>
-      <c r="H284">
+      <c r="H284" s="1">
+        <f t="shared" si="16"/>
+        <v>1118.2938779999999</v>
+      </c>
+      <c r="I284" s="1">
+        <f t="shared" si="17"/>
+        <v>1583.4249600000001</v>
+      </c>
+      <c r="J284" s="1">
+        <f t="shared" si="18"/>
+        <v>1456.7509632000001</v>
+      </c>
+      <c r="K284" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L284">
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>144</v>
       </c>
@@ -9347,11 +13911,27 @@
       <c r="G285" s="1">
         <v>413.99745000000001</v>
       </c>
-      <c r="H285">
+      <c r="H285" s="1">
+        <f t="shared" si="16"/>
+        <v>467.81711849999999</v>
+      </c>
+      <c r="I285" s="1">
+        <f t="shared" si="17"/>
+        <v>662.39592000000005</v>
+      </c>
+      <c r="J285" s="1">
+        <f t="shared" si="18"/>
+        <v>609.40424640000003</v>
+      </c>
+      <c r="K285" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L285">
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>148</v>
       </c>
@@ -9373,11 +13953,27 @@
       <c r="G286" s="1">
         <v>1400.8051499999999</v>
       </c>
-      <c r="H286">
+      <c r="H286" s="1">
+        <f t="shared" si="16"/>
+        <v>1582.9098194999997</v>
+      </c>
+      <c r="I286" s="1">
+        <f t="shared" si="17"/>
+        <v>2241.2882399999999</v>
+      </c>
+      <c r="J286" s="1">
+        <f t="shared" si="18"/>
+        <v>2061.9851807999999</v>
+      </c>
+      <c r="K286" s="6">
+        <f t="shared" si="19"/>
+        <v>1.472</v>
+      </c>
+      <c r="L286">
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>237</v>
       </c>
@@ -9399,11 +13995,27 @@
       <c r="G287" s="1">
         <v>1177.6982999999998</v>
       </c>
-      <c r="H287">
+      <c r="H287" s="1">
+        <f t="shared" si="16"/>
+        <v>1330.7990789999997</v>
+      </c>
+      <c r="I287" s="1">
+        <f t="shared" si="17"/>
+        <v>1884.3172799999998</v>
+      </c>
+      <c r="J287" s="1">
+        <f t="shared" si="18"/>
+        <v>1733.5718975999998</v>
+      </c>
+      <c r="K287" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L287">
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>258</v>
       </c>
@@ -9425,11 +14037,27 @@
       <c r="G288" s="1">
         <v>295.55879999999996</v>
       </c>
-      <c r="H288">
+      <c r="H288" s="1">
+        <f t="shared" si="16"/>
+        <v>333.98144399999995</v>
+      </c>
+      <c r="I288" s="1">
+        <f t="shared" si="17"/>
+        <v>472.89407999999997</v>
+      </c>
+      <c r="J288" s="1">
+        <f t="shared" si="18"/>
+        <v>435.0625536</v>
+      </c>
+      <c r="K288" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L288">
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>271</v>
       </c>
@@ -9451,11 +14079,27 @@
       <c r="G289" s="1">
         <v>4782.8617499999991</v>
       </c>
-      <c r="H289">
+      <c r="H289" s="1">
+        <f t="shared" si="16"/>
+        <v>5404.6337774999984</v>
+      </c>
+      <c r="I289" s="1">
+        <f t="shared" si="17"/>
+        <v>7652.5787999999993</v>
+      </c>
+      <c r="J289" s="1">
+        <f t="shared" si="18"/>
+        <v>7040.372496</v>
+      </c>
+      <c r="K289" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L289">
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>273</v>
       </c>
@@ -9477,11 +14121,27 @@
       <c r="G290" s="1">
         <v>2695.7919000000002</v>
       </c>
-      <c r="H290">
+      <c r="H290" s="1">
+        <f t="shared" si="16"/>
+        <v>3046.2448469999999</v>
+      </c>
+      <c r="I290" s="1">
+        <f t="shared" si="17"/>
+        <v>4313.2670400000006</v>
+      </c>
+      <c r="J290" s="1">
+        <f t="shared" si="18"/>
+        <v>3968.2056768000007</v>
+      </c>
+      <c r="K290" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L290">
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>332</v>
       </c>
@@ -9503,11 +14163,27 @@
       <c r="G291" s="1">
         <v>857.82555000000002</v>
       </c>
-      <c r="H291">
+      <c r="H291" s="1">
+        <f t="shared" si="16"/>
+        <v>969.34287149999989</v>
+      </c>
+      <c r="I291" s="1">
+        <f t="shared" si="17"/>
+        <v>1372.52088</v>
+      </c>
+      <c r="J291" s="1">
+        <f t="shared" si="18"/>
+        <v>1262.7192096000001</v>
+      </c>
+      <c r="K291" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L291">
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>336</v>
       </c>
@@ -9529,11 +14205,27 @@
       <c r="G292" s="1">
         <v>425.28644999999995</v>
       </c>
-      <c r="H292">
+      <c r="H292" s="1">
+        <f t="shared" si="16"/>
+        <v>480.57368849999989</v>
+      </c>
+      <c r="I292" s="1">
+        <f t="shared" si="17"/>
+        <v>680.45831999999996</v>
+      </c>
+      <c r="J292" s="1">
+        <f t="shared" si="18"/>
+        <v>626.02165439999999</v>
+      </c>
+      <c r="K292" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L292">
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>374</v>
       </c>
@@ -9555,11 +14247,27 @@
       <c r="G293" s="1">
         <v>2264.24325</v>
       </c>
-      <c r="H293">
+      <c r="H293" s="1">
+        <f t="shared" si="16"/>
+        <v>2558.5948724999998</v>
+      </c>
+      <c r="I293" s="1">
+        <f t="shared" si="17"/>
+        <v>3622.7892000000002</v>
+      </c>
+      <c r="J293" s="1">
+        <f t="shared" si="18"/>
+        <v>3332.9660640000002</v>
+      </c>
+      <c r="K293" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L293">
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>398</v>
       </c>
@@ -9581,11 +14289,27 @@
       <c r="G294" s="1">
         <v>590.16974999999991</v>
       </c>
-      <c r="H294">
+      <c r="H294" s="1">
+        <f t="shared" si="16"/>
+        <v>666.89181749999989</v>
+      </c>
+      <c r="I294" s="1">
+        <f t="shared" si="17"/>
+        <v>944.27159999999992</v>
+      </c>
+      <c r="J294" s="1">
+        <f t="shared" si="18"/>
+        <v>868.729872</v>
+      </c>
+      <c r="K294" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L294">
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>14</v>
       </c>
@@ -9607,14 +14331,30 @@
       <c r="G295" s="1">
         <v>244.55595</v>
       </c>
-      <c r="H295" s="4">
+      <c r="H295" s="1">
+        <f t="shared" si="16"/>
+        <v>276.34822349999996</v>
+      </c>
+      <c r="I295" s="1">
+        <f t="shared" si="17"/>
+        <v>391.28952000000004</v>
+      </c>
+      <c r="J295" s="1">
+        <f t="shared" si="18"/>
+        <v>359.98635840000003</v>
+      </c>
+      <c r="K295" s="6">
+        <f t="shared" si="19"/>
+        <v>1.4720000000000002</v>
+      </c>
+      <c r="L295" s="4">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
-  <sortState ref="A2:H295">
-    <sortCondition descending="1" ref="H2:H295"/>
+  <autoFilter ref="A1:L1"/>
+  <sortState ref="A2:L295">
+    <sortCondition descending="1" ref="L2:L295"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
